--- a/src/attributions/attributions_saliency_traj_93.xlsx
+++ b/src/attributions/attributions_saliency_traj_93.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.002197182737290859</v>
+        <v>9.76304176392162e-11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01470100600272417</v>
+        <v>2.571790558292264e-10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00112452800385654</v>
+        <v>1.079143510662739e-10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004477294161915779</v>
+        <v>3.593683406410975e-10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004893937613815069</v>
+        <v>4.142661491624011e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008104401640594006</v>
+        <v>5.491559429415815e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001007816405035555</v>
+        <v>1.497260371241538e-10</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009184668771922588</v>
+        <v>3.027712455749842e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01850287616252899</v>
+        <v>3.636465573109149e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003929649014025927</v>
+        <v>9.44992972762293e-11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01138195488601923</v>
+        <v>6.000992480714729e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003445066977292299</v>
+        <v>2.69499474819801e-11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009668821468949318</v>
+        <v>4.580263390785433e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004746185149997473</v>
+        <v>6.069929558982778e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>0.007334728725254536</v>
+        <v>6.608062985691276e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002170276828110218</v>
+        <v>1.791876091949973e-10</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.005810567177832127</v>
+        <v>2.675613897107354e-10</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01563357561826706</v>
+        <v>3.119558500408459e-10</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001175550743937492</v>
+        <v>1.446199271448734e-10</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003194252494722605</v>
+        <v>5.928005308852846e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004710161592811346</v>
+        <v>7.24442381083712e-12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008142917649820447</v>
+        <v>1.855041675824509e-10</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0004340833402238786</v>
+        <v>1.08450075309019e-10</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004686859436333179</v>
+        <v>1.428058088448481e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.299855547491461e-05</v>
+        <v>1.250462233759464e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0009930422529578209</v>
+        <v>4.288927199502801e-11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001151434727944434</v>
+        <v>5.731573549105917e-11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002635821932926774</v>
+        <v>1.297981166992201e-10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.001018702518194914</v>
+        <v>1.121532450243379e-10</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.005596831906586885</v>
+        <v>2.726978642897393e-10</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001488667097873986</v>
+        <v>3.638534196159782e-10</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001200938131660223</v>
+        <v>2.565417878130916e-10</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002020303159952164</v>
+        <v>9.270905224068038e-12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002580555155873299</v>
+        <v>3.773124868100552e-11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.002933409297838807</v>
+        <v>4.597671410255799e-10</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0007605702849105</v>
+        <v>3.148900307170521e-10</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.001973774284124374</v>
+        <v>1.569182978000683e-10</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001781381200999022</v>
+        <v>4.245324577989429e-11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001800962490960956</v>
+        <v>9.103402753840584e-11</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0006208561826497316</v>
+        <v>5.116926327097815e-11</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.002356456592679024</v>
+        <v>2.319057029742666e-10</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0003437655977904797</v>
+        <v>4.376573756181834e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.001894298009574413</v>
+        <v>2.671813603694062e-10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.002819794928655028</v>
+        <v>1.408299952349035e-11</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002292407210916281</v>
+        <v>6.705237060034008e-11</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.002130839042365551</v>
+        <v>7.46932585227178e-11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01517044007778168</v>
+        <v>9.695576563828467e-10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.001035744207911193</v>
+        <v>6.231636734410628e-12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0008977926918305457</v>
+        <v>1.638010282967173e-10</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01226398441940546</v>
+        <v>2.696228518228594e-10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.001280205557122827</v>
+        <v>8.292058012449033e-11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.004223289899528027</v>
+        <v>2.27230560756464e-12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.859810436144471e-05</v>
+        <v>1.241240443761171e-10</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.004036882892251015</v>
+        <v>1.478266120624738e-10</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.001153687131591141</v>
+        <v>7.45623771059023e-11</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.002016504760831594</v>
+        <v>2.660325570946753e-10</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0005538632394745946</v>
+        <v>2.866440765303402e-11</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0001947272685356438</v>
+        <v>3.862696829060042e-10</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002549298806115985</v>
+        <v>4.037813694512948e-10</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.007452248595654964</v>
+        <v>2.0638790676486e-10</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.00145222048740834</v>
+        <v>7.121477019200739e-12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.002605948830023408</v>
+        <v>9.560585656487319e-11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01305309776216745</v>
+        <v>3.585946470319179e-11</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.001166918082162738</v>
+        <v>1.64164626337282e-10</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.000924935273360461</v>
+        <v>3.142141824508116e-10</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001527933054603636</v>
+        <v>3.507430110238907e-11</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0006882771267555654</v>
+        <v>5.704296757169658e-11</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01176565140485764</v>
+        <v>3.181855334766226e-10</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.001375659834593534</v>
+        <v>2.428432177570272e-10</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004399110563099384</v>
+        <v>4.083146321054443e-10</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.000430839485488832</v>
+        <v>9.62812399252222e-11</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.004834424704313278</v>
+        <v>2.211907323967921e-10</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0009512322722002864</v>
+        <v>7.633026155584588e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.008133316412568092</v>
+        <v>3.311698415497943e-10</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.003246520413085818</v>
+        <v>9.554029789526908e-11</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.001241477439180017</v>
+        <v>8.434393461431711e-11</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.002013628138229251</v>
+        <v>2.253991437939362e-10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.971586607396603e-05</v>
+        <v>2.106403246271427e-10</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.000472454383270815</v>
+        <v>1.202976190883831e-10</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0009401929564774036</v>
+        <v>9.048586185889107e-11</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.001275325426831841</v>
+        <v>9.606621748092792e-11</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0004166954604443163</v>
+        <v>6.799737856111321e-11</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.002263878006488085</v>
+        <v>1.010046005167631e-10</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.001385219860821962</v>
+        <v>1.781372792331037e-11</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0003872551314998418</v>
+        <v>1.777778202427527e-10</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0008198324358090758</v>
+        <v>9.815787072042781e-11</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0005619912408292294</v>
+        <v>1.522975912049418e-10</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001314380206167698</v>
+        <v>1.161919935266376e-10</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.001736477366648614</v>
+        <v>1.100642407075858e-11</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.004367425106465816</v>
+        <v>1.029054064183299e-10</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.00613036472350359</v>
+        <v>2.134362964145708e-10</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.001914943335577846</v>
+        <v>5.384750423331752e-10</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0003840735298581421</v>
+        <v>5.250015699953536e-11</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.005476954393088818</v>
+        <v>2.950295563408645e-10</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.004244452342391014</v>
+        <v>3.303831097589693e-10</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.002667474560439587</v>
+        <v>2.254035291748835e-10</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.001743469736538827</v>
+        <v>6.343928854457559e-12</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.00564634008333087</v>
+        <v>4.677671444630604e-12</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.001652894075959921</v>
+        <v>5.834442651231342e-11</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0003855589893646538</v>
+        <v>1.211693800851066e-10</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.002652626484632492</v>
+        <v>1.076760625107198e-10</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.001080830348655581</v>
+        <v>2.421200046009986e-11</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0002347999543417245</v>
+        <v>1.500403135068495e-10</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.000531989149749279</v>
+        <v>3.71360928119735e-11</v>
       </c>
       <c r="DA2" t="n">
-        <v>8.118833648040891e-05</v>
+        <v>1.727700760234541e-10</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.001281793927773833</v>
+        <v>5.411729050996961e-11</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.001559057389385998</v>
+        <v>6.917510314563557e-11</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.00341623043641448</v>
+        <v>1.097431173713304e-10</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001469287555664778</v>
+        <v>1.182877268357529e-10</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0004865564405918121</v>
+        <v>4.421290417111479e-11</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.003155775601044297</v>
+        <v>7.611195007584115e-11</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.001444573746994138</v>
+        <v>3.445701710069748e-11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0003444232861511409</v>
+        <v>1.595485132899199e-10</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0009301613899879158</v>
+        <v>6.496716359327692e-11</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.002348656300455332</v>
+        <v>2.162892365209501e-10</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.007699355483055115</v>
+        <v>1.604575083913318e-10</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.001286535174585879</v>
+        <v>1.684190981121603e-11</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.00105671922210604</v>
+        <v>4.508692030835704e-11</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0006949357921257615</v>
+        <v>1.968918951489318e-11</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.00190498516894877</v>
+        <v>3.031754708393564e-11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.001273403526283801</v>
+        <v>3.816192917227568e-10</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0004568524891510606</v>
+        <v>1.773661079118583e-10</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0006068070651963353</v>
+        <v>2.266474508072491e-10</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.002778603695333004</v>
+        <v>1.214452705067259e-10</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0006212172447703779</v>
+        <v>1.545925748525079e-10</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.00310213677585125</v>
+        <v>6.893396270468699e-11</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.000426330283517018</v>
+        <v>1.222372481013423e-10</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.004870300181210041</v>
+        <v>1.747200717439057e-10</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0007655880763195455</v>
+        <v>7.870454288294582e-11</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002307283692061901</v>
+        <v>1.52215545723422e-10</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0002739006013143808</v>
+        <v>1.075614423917681e-11</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.002313196891918778</v>
+        <v>1.838594415604078e-10</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.001687836600467563</v>
+        <v>9.962354552417452e-11</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.003762399312108755</v>
+        <v>2.626700523755687e-10</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0008422406390309334</v>
+        <v>1.079400943626574e-10</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001165084075182676</v>
+        <v>1.52596962843532e-10</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.002332380274310708</v>
+        <v>3.368028078654106e-11</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.002345012500882149</v>
+        <v>3.905430492889828e-11</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0008320336928591132</v>
+        <v>1.687958106622034e-10</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0005429810262285173</v>
+        <v>1.195952642474296e-10</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.813904964365065e-05</v>
+        <v>8.631995118690838e-11</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002832681871950626</v>
+        <v>7.172799160182208e-11</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0005733330035582185</v>
+        <v>7.264301660203643e-11</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.004360349848866463</v>
+        <v>7.400812601643381e-11</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0008539253030903637</v>
+        <v>4.686250693053395e-11</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.002526266500353813</v>
+        <v>5.48216090578979e-11</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.00118266511708498</v>
+        <v>5.408814368612624e-11</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.00074890156975016</v>
+        <v>5.955333448603994e-11</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.003388633485883474</v>
+        <v>1.492653639578734e-10</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.002929390175268054</v>
+        <v>1.531607618510122e-10</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002608932321891189</v>
+        <v>9.953084884051222e-11</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.003182621207088232</v>
+        <v>1.544866456981708e-10</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003481770167127252</v>
+        <v>6.657061013548571e-11</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0002469988539814949</v>
+        <v>1.157585277633544e-10</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.003117293119430542</v>
+        <v>1.473064864532247e-10</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0009360573021695018</v>
+        <v>2.508975839587979e-11</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0008531403727829456</v>
+        <v>1.625385104286892e-10</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.000161982185090892</v>
+        <v>7.750770858461209e-11</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0008931620395742357</v>
+        <v>1.250334835667388e-10</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001408530515618622</v>
+        <v>7.768884147107968e-11</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001037158188410103</v>
+        <v>2.938460585966141e-11</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.003520111786201596</v>
+        <v>7.674003099644722e-11</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0001891020510811359</v>
+        <v>1.67655417326884e-10</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0009602524805814028</v>
+        <v>1.046894584910696e-10</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.001156927086412907</v>
+        <v>2.544888605404694e-11</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002401224337518215</v>
+        <v>8.830275399773768e-11</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.005291232373565435</v>
+        <v>6.745138475539036e-11</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0005869920132681727</v>
+        <v>1.372917057818057e-10</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0005436500068753958</v>
+        <v>1.261872550895049e-12</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.001508030225522816</v>
+        <v>1.908185970345144e-10</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.000473018764751032</v>
+        <v>1.49083995149013e-10</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.001019554445520043</v>
+        <v>3.100711631898179e-10</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.002338862046599388</v>
+        <v>3.563646322479741e-10</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.001123370137065649</v>
+        <v>1.457741011234859e-10</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.001230697729624808</v>
+        <v>1.177910963212625e-10</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.003916291054338217</v>
+        <v>1.846602037947065e-10</v>
       </c>
       <c r="FU2" t="n">
-        <v>7.669078331673518e-05</v>
+        <v>7.526128331658555e-11</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.006079701706767082</v>
+        <v>1.899276846906162e-10</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0004634053912013769</v>
+        <v>1.048594266972458e-10</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0003328084421809763</v>
+        <v>4.43774704483868e-11</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.002473288215696812</v>
+        <v>1.314499065152575e-10</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.001287231803871691</v>
+        <v>2.874996941903962e-11</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0008256395813077688</v>
+        <v>5.983318007718452e-11</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.003265263047069311</v>
+        <v>9.212483553788786e-11</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.001548272557556629</v>
+        <v>1.272853766831616e-10</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.003783971536904573</v>
+        <v>1.817652139912695e-10</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.002703017089515924</v>
+        <v>5.962105115164817e-11</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0005961038405075669</v>
+        <v>9.768712921909284e-11</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0006036674021743238</v>
+        <v>5.003893133181947e-11</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.002676642034202814</v>
+        <v>2.573170496122934e-11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06291462481021881</v>
+        <v>8.731482550872194e-12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007851956412196159</v>
+        <v>1.359470695738718e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01926598139107227</v>
+        <v>4.122732016886843e-11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00480373203754425</v>
+        <v>3.937640144502375e-13</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002983855083584785</v>
+        <v>8.266249663935188e-12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01629071310162544</v>
+        <v>3.001261045243453e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009888146072626114</v>
+        <v>5.840958272607111e-11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007429484277963638</v>
+        <v>3.627884104240309e-11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01129540801048279</v>
+        <v>2.01795975762753e-11</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04993882030248642</v>
+        <v>2.306312259225951e-12</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009877054952085018</v>
+        <v>1.261938643859484e-11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02900390140712261</v>
+        <v>1.920016402812141e-11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01140040718019009</v>
+        <v>5.372837591499646e-13</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01415239274501801</v>
+        <v>1.697475710341068e-13</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01476407796144485</v>
+        <v>3.452189922814597e-11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000594395911321044</v>
+        <v>5.145880249690649e-11</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004309359937906265</v>
+        <v>3.442589963098541e-11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007595892064273357</v>
+        <v>1.853379602567706e-11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01055878959596157</v>
+        <v>1.271436515098978e-11</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003486641217023134</v>
+        <v>1.080725526431126e-11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006506329402327538</v>
+        <v>2.876827595588161e-11</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01021679490804672</v>
+        <v>4.586359937663875e-12</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01071799173951149</v>
+        <v>1.349249488177828e-13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000458520429674536</v>
+        <v>6.020034297449239e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005224571563303471</v>
+        <v>5.203382429791459e-12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003070375649258494</v>
+        <v>1.78749098855846e-11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00706902239471674</v>
+        <v>5.855800566667568e-11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01408017240464687</v>
+        <v>3.081629049161982e-11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.008866086602210999</v>
+        <v>1.977549547726998e-11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003273553214967251</v>
+        <v>3.52285839388955e-11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.002251852303743362</v>
+        <v>3.265294631904503e-11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002446662168949842</v>
+        <v>2.714175672408059e-12</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.22159568592906e-05</v>
+        <v>7.753737756022172e-12</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.01327828783541918</v>
+        <v>1.068131260523186e-11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001755442644935101</v>
+        <v>8.618912875069107e-12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.005072783678770065</v>
+        <v>4.67788481561815e-12</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.007742507383227348</v>
+        <v>8.148058616708198e-12</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0005145889008417726</v>
+        <v>8.741026999437018e-12</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.005943446420133114</v>
+        <v>2.509014003504451e-11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.003665287746116519</v>
+        <v>2.313681017607205e-11</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.00261736148968339</v>
+        <v>2.088603075212081e-11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001582703087478876</v>
+        <v>2.516245545258755e-11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001497016055509448</v>
+        <v>6.941954823480589e-12</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.004446629900485277</v>
+        <v>1.000346333546176e-11</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00648416904732585</v>
+        <v>2.660672897281113e-12</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0418308787047863</v>
+        <v>4.436825559728241e-11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.00691823149099946</v>
+        <v>1.903879137676867e-11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.01073961332440376</v>
+        <v>2.091582983199114e-11</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.00964589137583971</v>
+        <v>2.839517163066851e-11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0006925826892256737</v>
+        <v>2.8419868888796e-11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01742888987064362</v>
+        <v>1.018618522863335e-11</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.002840186702087522</v>
+        <v>1.403197957133839e-11</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.002472108695656061</v>
+        <v>1.263377336774285e-11</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005734981968998909</v>
+        <v>2.60556506925802e-12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01628382876515388</v>
+        <v>2.885513225928116e-12</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01549089327454567</v>
+        <v>2.534538204312931e-11</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.007752100471407175</v>
+        <v>2.229884679683103e-11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01273346412926912</v>
+        <v>4.883169563152379e-11</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.003792742500081658</v>
+        <v>2.494065891311958e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.003363244934007525</v>
+        <v>2.553230890600666e-11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.003696734085679054</v>
+        <v>1.945195046704207e-11</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.004938366822898388</v>
+        <v>7.168510229860203e-11</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.003709201235324144</v>
+        <v>3.651255513215101e-12</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.003623900003731251</v>
+        <v>2.057515789688491e-11</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.003370295045897365</v>
+        <v>1.593316104053777e-11</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.003906331025063992</v>
+        <v>1.588671251842588e-12</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01247604563832283</v>
+        <v>3.473870496817355e-11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.00701481755822897</v>
+        <v>5.162463338759249e-12</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.007178280036896467</v>
+        <v>2.748624071402528e-11</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.01655481941998005</v>
+        <v>1.218913598527438e-11</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0007916155736893415</v>
+        <v>9.301671845957094e-13</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001598670147359371</v>
+        <v>1.400140940688299e-11</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01990953274071217</v>
+        <v>1.680594725883555e-11</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.008578408509492874</v>
+        <v>9.593140518071586e-12</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.004945576190948486</v>
+        <v>2.62701804754073e-11</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004858569242060184</v>
+        <v>1.483118315659393e-11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0001560533419251442</v>
+        <v>7.651232078464965e-12</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.007339333184063435</v>
+        <v>4.849173146359576e-11</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.00754594849422574</v>
+        <v>6.195198434116866e-13</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001601272379048169</v>
+        <v>6.488039272500856e-12</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0004148904117755592</v>
+        <v>3.517715632672669e-13</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.01111866626888514</v>
+        <v>1.410634196258309e-11</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.003885925048962235</v>
+        <v>1.627767018397286e-11</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.001605863450095057</v>
+        <v>1.009976650923061e-11</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0009452616795897484</v>
+        <v>2.167009627296324e-12</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0007924630772322416</v>
+        <v>2.204448863035724e-12</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.004567216150462627</v>
+        <v>5.283311114989697e-12</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001454985816963017</v>
+        <v>2.137224425213802e-12</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.002144670346751809</v>
+        <v>3.686407949732295e-12</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.01138958148658276</v>
+        <v>2.942139240569297e-11</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.008847663179039955</v>
+        <v>4.445799631214165e-11</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001062854571500793</v>
+        <v>1.352434917528678e-11</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.01658603735268116</v>
+        <v>3.001776952005208e-11</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01306168362498283</v>
+        <v>4.518252091911812e-11</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001530249137431383</v>
+        <v>1.462412829722481e-11</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.003923847805708647</v>
+        <v>1.89195412808596e-11</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0006615739548578858</v>
+        <v>3.22762198912141e-11</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001041424577124417</v>
+        <v>2.287639175313494e-11</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001193917589262128</v>
+        <v>2.027470205612225e-12</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.01049742475152016</v>
+        <v>2.922667967017456e-12</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004386082757264376</v>
+        <v>1.731066331944753e-11</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.005826829932630062</v>
+        <v>8.799151511584835e-12</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.003374757478013635</v>
+        <v>6.806761317784682e-12</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0005737001774832606</v>
+        <v>3.477769721510482e-12</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.005304684396833181</v>
+        <v>2.005273334534929e-12</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001021848642267287</v>
+        <v>1.476744941608654e-12</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.002752469619736075</v>
+        <v>1.068496528235097e-12</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.00725703127682209</v>
+        <v>9.081176782776978e-12</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.003781178034842014</v>
+        <v>1.254554793383988e-11</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.003466962836682796</v>
+        <v>5.657676410697476e-11</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.00258515146560967</v>
+        <v>6.340695329898338e-11</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.003238766919821501</v>
+        <v>3.557911604223918e-11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.002312399446964264</v>
+        <v>1.897199931877314e-11</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.005140393041074276</v>
+        <v>4.904610398370757e-11</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.009450624696910381</v>
+        <v>1.126315013477708e-11</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.006360331550240517</v>
+        <v>1.521784000896309e-12</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.008477079682052135</v>
+        <v>1.69477071265689e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.001410310389474034</v>
+        <v>1.286965152502706e-11</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.006945824716240168</v>
+        <v>8.574222928880992e-12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.004306789021939039</v>
+        <v>3.139645661509594e-12</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.005186002235859632</v>
+        <v>2.891500407165015e-11</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.002406086307018995</v>
+        <v>1.922311962387901e-11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.00316143874078989</v>
+        <v>2.590642284028277e-11</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0004736646078526974</v>
+        <v>1.815038050412277e-11</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00372991943731904</v>
+        <v>1.000798749428711e-11</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0008486201404593885</v>
+        <v>1.132690382460444e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0147324800491333</v>
+        <v>5.78579684162861e-11</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0003000034776050597</v>
+        <v>3.0544983209424e-11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.005323608871549368</v>
+        <v>3.569675111059212e-11</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.00592177826911211</v>
+        <v>1.449814834159069e-11</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001852419460192323</v>
+        <v>2.174084003103705e-11</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.000920799735467881</v>
+        <v>1.93271613990742e-11</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.00630151154473424</v>
+        <v>2.034063672703978e-12</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.00117273791693151</v>
+        <v>2.079902569618319e-11</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0004265679745003581</v>
+        <v>4.821359977924544e-11</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00855609867721796</v>
+        <v>2.663307942241122e-11</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.003473855089396238</v>
+        <v>1.661619800086278e-11</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.003086668439209461</v>
+        <v>1.624224192642298e-12</v>
       </c>
       <c r="EJ5" t="n">
-        <v>2.002157270908356e-05</v>
+        <v>1.893554757437244e-13</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.001195107470266521</v>
+        <v>8.733370797375795e-12</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.009130467660725117</v>
+        <v>1.861278839387914e-11</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.00077817402780056</v>
+        <v>1.123084264476049e-12</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.000309434806695208</v>
+        <v>8.427325677573538e-13</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.006240691523998976</v>
+        <v>8.904934081788163e-12</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.005837966222316027</v>
+        <v>1.870840721923672e-13</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.007641651667654514</v>
+        <v>1.077778491453962e-11</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.00552262319251895</v>
+        <v>4.096289279997833e-12</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.008537513203918934</v>
+        <v>2.40946047835866e-11</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0008465307764708996</v>
+        <v>2.124021444838142e-11</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.005060906521975994</v>
+        <v>1.674948374441598e-11</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.005761375650763512</v>
+        <v>1.545163649807613e-11</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0006123872008174658</v>
+        <v>1.922921370745012e-11</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.003118850523605943</v>
+        <v>2.394836065566786e-12</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.01134834066033363</v>
+        <v>1.247115084812567e-11</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.002642727922648191</v>
+        <v>1.850734843156232e-11</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.002953191753476858</v>
+        <v>1.312104418171867e-11</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004517857450991869</v>
+        <v>1.100117913432896e-11</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.002162936609238386</v>
+        <v>5.371591192682157e-12</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.006081072613596916</v>
+        <v>1.564134997737721e-12</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.002555564511567354</v>
+        <v>3.097599433898868e-12</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.003650611732155085</v>
+        <v>1.232833713588066e-12</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.003865610342472792</v>
+        <v>1.404479831046412e-11</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001045469660311937</v>
+        <v>3.394112421672979e-11</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.006544294767081738</v>
+        <v>1.07915499453215e-12</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.003753144294023514</v>
+        <v>3.816215139035295e-12</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.009640101343393326</v>
+        <v>4.388878149796938e-12</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.00546647934243083</v>
+        <v>2.619889027943856e-11</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0007321698940359056</v>
+        <v>7.167805845392783e-12</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.006051946897059679</v>
+        <v>4.267684122760684e-11</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.006633526645600796</v>
+        <v>4.434702952083036e-11</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.008294151164591312</v>
+        <v>1.552750636402145e-11</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.01165605243295431</v>
+        <v>7.755403957920848e-11</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.004162175580859184</v>
+        <v>2.889774530778766e-11</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.004332254640758038</v>
+        <v>2.678073041106899e-12</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01353353075683117</v>
+        <v>2.63648269882566e-11</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.005245252978056669</v>
+        <v>3.333268036587178e-11</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004275485407561064</v>
+        <v>3.712782165044004e-11</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0143135879188776</v>
+        <v>7.085186604083304e-11</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003392463084310293</v>
+        <v>3.552069749446218e-11</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.01248396839946508</v>
+        <v>6.224435897261849e-12</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.003102938644587994</v>
+        <v>1.144104342515329e-12</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.003624393371865153</v>
+        <v>2.791864829598811e-11</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.002000644104555249</v>
+        <v>2.844563473658468e-11</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.003338456153869629</v>
+        <v>3.109575097415274e-11</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.009797144681215286</v>
+        <v>1.745758919369234e-11</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0136469341814518</v>
+        <v>2.908701057791063e-12</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.008498247712850571</v>
+        <v>9.001843541411869e-12</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.004627140704542398</v>
+        <v>1.650650102713591e-11</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01338135451078415</v>
+        <v>0.08293387293815613</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2876779437065125</v>
+        <v>0.3317940533161163</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003199849277734756</v>
+        <v>0.1202984377741814</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2175747603178024</v>
+        <v>0.1347886770963669</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02657694742083549</v>
+        <v>0.04675515368580818</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004196645691990852</v>
+        <v>0.1135568991303444</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04116190224885941</v>
+        <v>0.1388480663299561</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02204380184412003</v>
+        <v>0.05336595699191093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04547600448131561</v>
+        <v>0.1145776808261871</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04630676656961441</v>
+        <v>0.06548766791820526</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2478113025426865</v>
+        <v>0.4513272643089294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007814943790435791</v>
+        <v>0.1777274757623672</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1935975849628448</v>
+        <v>0.1906603425741196</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05999763309955597</v>
+        <v>0.0717741921544075</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03501420840620995</v>
+        <v>0.1009665876626968</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02124430611729622</v>
+        <v>0.07820874452590942</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03996224328875542</v>
+        <v>0.211496502161026</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03032897040247917</v>
+        <v>0.1050423160195351</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01373658049851656</v>
+        <v>0.003617629408836365</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03326387330889702</v>
+        <v>0.05318321660161018</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01338101737201214</v>
+        <v>0.06721949577331543</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01926138252019882</v>
+        <v>0.0299045518040657</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02869841456413269</v>
+        <v>0.05537708848714828</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01974463276565075</v>
+        <v>0.07372605800628662</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0418093204498291</v>
+        <v>0.006329946685582399</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03117541782557964</v>
+        <v>0.01083583291620016</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02577736414968967</v>
+        <v>0.1022123768925667</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0469229519367218</v>
+        <v>0.06027279794216156</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03028169274330139</v>
+        <v>0.01013880595564842</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.007475825492292643</v>
+        <v>0.002858527004718781</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006724309176206589</v>
+        <v>0.1837348639965057</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02639546059072018</v>
+        <v>0.008161142468452454</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.03348115459084511</v>
+        <v>0.1652598232030869</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01788219250738621</v>
+        <v>0.02991556935012341</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.027895487844944</v>
+        <v>0.05671902000904083</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004924546927213669</v>
+        <v>0.0008525550365447998</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00790124200284481</v>
+        <v>0.01298640668392181</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0195075049996376</v>
+        <v>0.1325904279947281</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.008373679593205452</v>
+        <v>0.03082847595214844</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.006684195250272751</v>
+        <v>0.04928721860051155</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.009706554003059864</v>
+        <v>0.1021220833063126</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01207839231938124</v>
+        <v>0.03788655251264572</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0227404423058033</v>
+        <v>0.003675926476716995</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01664630509912968</v>
+        <v>0.007748934905976057</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.00952954962849617</v>
+        <v>0.002865063026547432</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.04003091901540756</v>
+        <v>0.02803603187203407</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1713288426399231</v>
+        <v>0.240663468837738</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.03894352540373802</v>
+        <v>0.05158017203211784</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.06257995218038559</v>
+        <v>0.1051898524165154</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.004824605770409107</v>
+        <v>0.09704731404781342</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01970211043953896</v>
+        <v>0.02021561935544014</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003856332739815116</v>
+        <v>0.03331615030765533</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03081298246979713</v>
+        <v>0.03857275098562241</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005805870518088341</v>
+        <v>0.0257827490568161</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.01087633147835732</v>
+        <v>0.07225209474563599</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05984244495630264</v>
+        <v>0.1117488592863083</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.05625789240002632</v>
+        <v>0.1411958932876587</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.04238117858767509</v>
+        <v>0.1372686475515366</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.04769353196024895</v>
+        <v>0.1569502949714661</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006992608308792114</v>
+        <v>0.09775598347187042</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.03629975765943527</v>
+        <v>0.00348857045173645</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.04378335922956467</v>
+        <v>0.0405719019472599</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01251810323446989</v>
+        <v>0.1235309094190598</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.04192723333835602</v>
+        <v>0.01042765565216541</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002785959979519248</v>
+        <v>0.08856599032878876</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001630673883482814</v>
+        <v>0.01853955537080765</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01508290600031614</v>
+        <v>0.05671080201864243</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02726004645228386</v>
+        <v>0.03833658993244171</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0241120308637619</v>
+        <v>0.02004330605268478</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.00493680639192462</v>
+        <v>0.002282094210386276</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02715788036584854</v>
+        <v>0.02998785860836506</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.009062136523425579</v>
+        <v>0.002749139908701181</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0252427663654089</v>
+        <v>0.01911985129117966</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.08812942355871201</v>
+        <v>0.173858642578125</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01271258201450109</v>
+        <v>0.01482414826750755</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.03675071895122528</v>
+        <v>0.02939677610993385</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02648786269128323</v>
+        <v>0.01639007031917572</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.008029616437852383</v>
+        <v>0.05718784779310226</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.01966993138194084</v>
+        <v>0.005849461071193218</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.003998119384050369</v>
+        <v>0.07224416732788086</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01240590400993824</v>
+        <v>0.07322561740875244</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.01020957436412573</v>
+        <v>0.01103328168392181</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.04022573307156563</v>
+        <v>0.1209919154644012</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.01735616102814674</v>
+        <v>0.03595839068293571</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02722555957734585</v>
+        <v>0.06066645309329033</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01122325100004673</v>
+        <v>0.03309973329305649</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005812071263790131</v>
+        <v>0.003668847493827343</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.008166933432221413</v>
+        <v>0.008798464201390743</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0009750537574291229</v>
+        <v>0.02519553899765015</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01630330830812454</v>
+        <v>0.01554367691278458</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.05012381821870804</v>
+        <v>0.03738272935152054</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003167886286973953</v>
+        <v>0.06897690147161484</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.002292038640007377</v>
+        <v>0.07379871606826782</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.05491703748703003</v>
+        <v>0.2345795631408691</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.05081404000520706</v>
+        <v>0.1372046172618866</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.01253231707960367</v>
+        <v>0.002671073190867901</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.03684628009796143</v>
+        <v>0.09226845949888229</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.04083635658025742</v>
+        <v>0.02690576575696468</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.003869364038109779</v>
+        <v>0.06049682945013046</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.005143217742443085</v>
+        <v>0.01268862560391426</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.04042371362447739</v>
+        <v>0.1269893497228622</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0236945915967226</v>
+        <v>0.03764219209551811</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03672231733798981</v>
+        <v>0.06755228340625763</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01463727466762066</v>
+        <v>0.02086108364164829</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.007870950736105442</v>
+        <v>0.01683273166418076</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01102122105658054</v>
+        <v>0.006812406703829765</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.006327283568680286</v>
+        <v>0.01857532188296318</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01263197045773268</v>
+        <v>0.03396936133503914</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.01189146470278502</v>
+        <v>0.01390930917114019</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01027327589690685</v>
+        <v>0.06664445996284485</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.02835986949503422</v>
+        <v>0.0908983051776886</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.08743949979543686</v>
+        <v>0.0516166128218174</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02533295378088951</v>
+        <v>0.07877127826213837</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001396369189023972</v>
+        <v>0.1350036114454269</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02774085476994514</v>
+        <v>0.02373890578746796</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0152175035327673</v>
+        <v>0.1612761616706848</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.02900909073650837</v>
+        <v>0.01843178272247314</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.01137954276055098</v>
+        <v>0.001013809815049171</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.005936973262578249</v>
+        <v>0.0070804413408041</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0171449389308691</v>
+        <v>0.01713861897587776</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.01256691385060549</v>
+        <v>0.04825073480606079</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.04163497686386108</v>
+        <v>0.01087738201022148</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.02555341459810734</v>
+        <v>0.0469471849501133</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.003896711161360145</v>
+        <v>0.0108335092663765</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.02471047639846802</v>
+        <v>0.03180649131536484</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.02432707883417606</v>
+        <v>0.1281114220619202</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0009805229492485523</v>
+        <v>0.02991500310599804</v>
       </c>
       <c r="DX7" t="n">
-        <v>3.1824572943151e-05</v>
+        <v>0.08246993273496628</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.02326422929763794</v>
+        <v>0.03236020356416702</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.02584988810122013</v>
+        <v>0.05461357906460762</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.005586890503764153</v>
+        <v>0.07182840257883072</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.007410514168441296</v>
+        <v>0.047245092689991</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.01520989276468754</v>
+        <v>0.01906591095030308</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001604098593816161</v>
+        <v>0.1154536232352257</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01054886169731617</v>
+        <v>0.09187062084674835</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.005251821130514145</v>
+        <v>0.02561390958726406</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0384553074836731</v>
+        <v>0.09996408224105835</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.03179709613323212</v>
+        <v>0.01617780141532421</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02754330448806286</v>
+        <v>0.03293263167142868</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0213116817176342</v>
+        <v>0.0035841497592628</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02079313062131405</v>
+        <v>0.01519094221293926</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.009753248654305935</v>
+        <v>0.003653215244412422</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.00442925002425909</v>
+        <v>0.004051139578223228</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.008585165254771709</v>
+        <v>0.009025808423757553</v>
       </c>
       <c r="EO7" t="n">
-        <v>4.222989082336426e-05</v>
+        <v>0.01308656763285398</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.03028666600584984</v>
+        <v>0.08353728801012039</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.03847163915634155</v>
+        <v>0.0006354330107569695</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01452770549803972</v>
+        <v>0.01669621840119362</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.007304694503545761</v>
+        <v>0.05422632396221161</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.003747105598449707</v>
+        <v>0.001058277557604015</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.01964389905333519</v>
+        <v>0.04351387172937393</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0298666600137949</v>
+        <v>0.0443691611289978</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0009225013200193644</v>
+        <v>0.06954822689294815</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.001659352332353592</v>
+        <v>0.005302682053297758</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.04200754687190056</v>
+        <v>0.1410500407218933</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.01528994552791119</v>
+        <v>0.0189133882522583</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02994515374302864</v>
+        <v>0.07839922606945038</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01490890886634588</v>
+        <v>0.01678290963172913</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.009528915397822857</v>
+        <v>0.006665437016636133</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01014703884720802</v>
+        <v>0.002250948920845985</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.001034644898027182</v>
+        <v>0.03229164332151413</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01907085999846458</v>
+        <v>0.03134737908840179</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0004068640992045403</v>
+        <v>0.02279292419552803</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02375978417694569</v>
+        <v>0.06713704764842987</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02048211731016636</v>
+        <v>0.05999418348073959</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03286155313253403</v>
+        <v>0.0864340215921402</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.005644232500344515</v>
+        <v>0.06220382452011108</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.04002071917057037</v>
+        <v>0.04837275668978691</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.01188462506979704</v>
+        <v>0.03565554693341255</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.008453143760561943</v>
+        <v>0.007192522287368774</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0184784010052681</v>
+        <v>0.09276314079761505</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.00271746888756752</v>
+        <v>0.0661885067820549</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.04936353862285614</v>
+        <v>0.1008782014250755</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0313132181763649</v>
+        <v>0.005011000670492649</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02148035913705826</v>
+        <v>0.01355176791548729</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.006340080872178078</v>
+        <v>0.1910084784030914</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.000197472982108593</v>
+        <v>0.008636413142085075</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.00186564214527607</v>
+        <v>0.04197853058576584</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.001642266288399696</v>
+        <v>0.005247261375188828</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.03492588177323341</v>
+        <v>0.06489583849906921</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.04958118498325348</v>
+        <v>0.003184789791703224</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01659896597266197</v>
+        <v>0.1256599426269531</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01310318522155285</v>
+        <v>0.05715329572558403</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.01092191226780415</v>
+        <v>0.00252959132194519</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.01583078689873219</v>
+        <v>0.03862372413277626</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.04981895536184311</v>
+        <v>0.02568474039435387</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.08005426824092865</v>
+        <v>0.08485835790634155</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.00824269000440836</v>
+        <v>0.03243546932935715</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02477885782718658</v>
+        <v>0.0003768664319068193</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.05820314213633537</v>
+        <v>0.5574753284454346</v>
       </c>
       <c r="B8" t="n">
-        <v>0.427114874124527</v>
+        <v>1.109179258346558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03133897855877876</v>
+        <v>0.07830314338207245</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2633202373981476</v>
+        <v>0.1293262839317322</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0621027946472168</v>
+        <v>0.1219776272773743</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3037694096565247</v>
+        <v>0.4306618571281433</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01634705252945423</v>
+        <v>0.01069460064172745</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09595222771167755</v>
+        <v>0.1657743155956268</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04628715664148331</v>
+        <v>0.08189353346824646</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1347532868385315</v>
+        <v>0.4051630795001984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3272359669208527</v>
+        <v>1.29026985168457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008197493851184845</v>
+        <v>0.2607821226119995</v>
       </c>
       <c r="M8" t="n">
-        <v>0.234705850481987</v>
+        <v>0.5745759606361389</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04895946756005287</v>
+        <v>0.1501200199127197</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3471284508705139</v>
+        <v>0.4010472297668457</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002648457884788513</v>
+        <v>0.09679848700761795</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007580909878015518</v>
+        <v>0.1250111758708954</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0532505214214325</v>
+        <v>0.03059650957584381</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03960704430937767</v>
+        <v>0.07829354703426361</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06112472712993622</v>
+        <v>0.288441926240921</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03545567020773888</v>
+        <v>0.03868201747536659</v>
       </c>
       <c r="V8" t="n">
-        <v>0.05692069232463837</v>
+        <v>0.1976126432418823</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0279327966272831</v>
+        <v>0.1654456257820129</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02557237073779106</v>
+        <v>0.0381445549428463</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.05690335854887962</v>
+        <v>0.07053110748529434</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03842366114258766</v>
+        <v>0.2360555380582809</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05055372789502144</v>
+        <v>0.008883319795131683</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002070460468530655</v>
+        <v>0.002672323957085609</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.04465112090110779</v>
+        <v>0.1701003909111023</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.02440403588116169</v>
+        <v>0.006680998951196671</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0005625202320516109</v>
+        <v>0.3599786758422852</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01799420639872551</v>
+        <v>0.4686067402362823</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.004050122573971748</v>
+        <v>0.2412310242652893</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.02441317215561867</v>
+        <v>0.06052560359239578</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03598549962043762</v>
+        <v>0.3678901493549347</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.037112046033144</v>
+        <v>0.1202700436115265</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03774325549602509</v>
+        <v>0.002547822892665863</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.07314363867044449</v>
+        <v>0.2406878620386124</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.02266141958534718</v>
+        <v>0.08473408967256546</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0004321467131376266</v>
+        <v>0.009389776736497879</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.02318612858653069</v>
+        <v>0.2245578467845917</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.05439485982060432</v>
+        <v>0.2148811817169189</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.009026544168591499</v>
+        <v>0.118064858019352</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.03928947076201439</v>
+        <v>0.378314733505249</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.06106070056557655</v>
+        <v>0.02219803631305695</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.03184117376804352</v>
+        <v>0.1962539851665497</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.272275298833847</v>
+        <v>1.139817237854004</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.02178372070193291</v>
+        <v>0.1297526508569717</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.04523279517889023</v>
+        <v>0.05962129682302475</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.04085651412606239</v>
+        <v>0.250834047794342</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.149662971496582</v>
+        <v>0.4377528131008148</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.02178179658949375</v>
+        <v>0.02626417391002178</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.05276514962315559</v>
+        <v>0.02307255379855633</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0865166112780571</v>
+        <v>0.01636584848165512</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.07230944186449051</v>
+        <v>0.1447689682245255</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07603241503238678</v>
+        <v>0.01342040300369263</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1234653815627098</v>
+        <v>0.07896358519792557</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.07960883527994156</v>
+        <v>0.1655979156494141</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.1045583337545395</v>
+        <v>0.2740149796009064</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.08581310510635376</v>
+        <v>0.1539599895477295</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01260006800293922</v>
+        <v>0.151961624622345</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.06867058575153351</v>
+        <v>0.09031261503696442</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.04049591720104218</v>
+        <v>0.06102675572037697</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.01394042931497097</v>
+        <v>0.1221541836857796</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.05365542322397232</v>
+        <v>0.08459648489952087</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.05508981272578239</v>
+        <v>0.01561068557202816</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.05432036146521568</v>
+        <v>0.0715285986661911</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02127132005989552</v>
+        <v>0.1100711897015572</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001950934529304504</v>
+        <v>0.05832752212882042</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.02064716070890427</v>
+        <v>0.1517426371574402</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.02723811753094196</v>
+        <v>0.04932954162359238</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.01280481275171041</v>
+        <v>0.008705552667379379</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.03160160407423973</v>
+        <v>0.0752611979842186</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1363173574209213</v>
+        <v>0.8575886487960815</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.06409593671560287</v>
+        <v>0.06307453662157059</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.08944448828697205</v>
+        <v>0.1268031299114227</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0501336045563221</v>
+        <v>0.1198671162128448</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.05731690302491188</v>
+        <v>0.2841894328594208</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.02934453636407852</v>
+        <v>0.1563750505447388</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.02981076948344707</v>
+        <v>0.1482585519552231</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.06873860210180283</v>
+        <v>0.03520495072007179</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.008654293604195118</v>
+        <v>0.1038911938667297</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0661480501294136</v>
+        <v>0.339138388633728</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.06202508509159088</v>
+        <v>0.01626797579228878</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0445738285779953</v>
+        <v>0.1080919578671455</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.02250472828745842</v>
+        <v>0.01437421143054962</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.05814843624830246</v>
+        <v>0.1611790210008621</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.01928051561117172</v>
+        <v>0.07393385469913483</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.01912199705839157</v>
+        <v>0.007042724639177322</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.03711248189210892</v>
+        <v>0.04791541770100594</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.04764892905950546</v>
+        <v>0.3027878999710083</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.007708967197686434</v>
+        <v>0.7742046713829041</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.01992723345756531</v>
+        <v>0.1122018322348595</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001715710386633873</v>
+        <v>0.2626356780529022</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0239369198679924</v>
+        <v>0.3683057427406311</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.003417892381548882</v>
+        <v>0.459111362695694</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.05558910220861435</v>
+        <v>0.02679372578859329</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.06198750436306</v>
+        <v>0.02314552292227745</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.02745396830141544</v>
+        <v>0.065106600522995</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001586017664521933</v>
+        <v>0.02986055612564087</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.05905310437083244</v>
+        <v>0.3264468610286713</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.05781860277056694</v>
+        <v>0.009527551010251045</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.06416304409503937</v>
+        <v>0.08485889434814453</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01552697643637657</v>
+        <v>0.07562894374132156</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0680822879076004</v>
+        <v>0.1314748972654343</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.01801540702581406</v>
+        <v>0.01623101904988289</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.04350678622722626</v>
+        <v>0.02932830899953842</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.01924116164445877</v>
+        <v>0.09171512722969055</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.03382318466901779</v>
+        <v>0.3822558522224426</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.04739577695727348</v>
+        <v>0.106058806180954</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.01762278005480766</v>
+        <v>0.05389152094721794</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1418601274490356</v>
+        <v>0.1171673312783241</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0103995930403471</v>
+        <v>0.2586706578731537</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.06254030019044876</v>
+        <v>0.1123310104012489</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.02669833041727543</v>
+        <v>0.1952080428600311</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.03486035019159317</v>
+        <v>0.003999797627329826</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.004771032370626926</v>
+        <v>0.2307948917150497</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.005835811607539654</v>
+        <v>0.04510969668626785</v>
       </c>
       <c r="DO8" t="n">
-        <v>4.237191751599312e-05</v>
+        <v>0.07272568345069885</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.03067848458886147</v>
+        <v>0.09875056892633438</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0475146695971489</v>
+        <v>0.1895345896482468</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01867482624948025</v>
+        <v>0.03311295062303543</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01909280382096767</v>
+        <v>0.006028838455677032</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05588211864233017</v>
+        <v>0.02956992387771606</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001527171581983566</v>
+        <v>0.2353241294622421</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.08440347015857697</v>
+        <v>0.002165701240301132</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0191228836774826</v>
+        <v>0.1292677968740463</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.03129398077726364</v>
+        <v>0.2035964578390121</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.08351793140172958</v>
+        <v>0.1927222907543182</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.005903306882828474</v>
+        <v>0.01722101867198944</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01009432226419449</v>
+        <v>0.1296784281730652</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03553570434451103</v>
+        <v>0.1128856539726257</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.01165065169334412</v>
+        <v>0.01383663341403008</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.04473041370511055</v>
+        <v>0.04362596943974495</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.03142294660210609</v>
+        <v>0.2529944777488708</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.02887651510536671</v>
+        <v>0.08852022141218185</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.04863578081130981</v>
+        <v>0.04955555126070976</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.04543042927980423</v>
+        <v>0.01213871873915195</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.007376119494438171</v>
+        <v>0.02198940701782703</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004759647883474827</v>
+        <v>0.1868817210197449</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.07944966107606888</v>
+        <v>0.02935424819588661</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.01857121661305428</v>
+        <v>0.01681127399206161</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.002579864580184221</v>
+        <v>0.0773904100060463</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.01104890555143356</v>
+        <v>0.0464395210146904</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0004507210105657578</v>
+        <v>0.01497401669621468</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.02628185227513313</v>
+        <v>0.1586714237928391</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.06223439425230026</v>
+        <v>0.04974984750151634</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03330141678452492</v>
+        <v>0.1065640598535538</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02107765898108482</v>
+        <v>0.3277325630187988</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.04696949943900108</v>
+        <v>0.09581020474433899</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03975817561149597</v>
+        <v>0.02394960075616837</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.08019483089447021</v>
+        <v>0.1042222529649734</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.005158334970474243</v>
+        <v>0.06835943460464478</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.004233862273395061</v>
+        <v>0.07340977340936661</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.05664365738630295</v>
+        <v>0.3787517845630646</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.04810936748981476</v>
+        <v>0.01899519935250282</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05849950015544891</v>
+        <v>0.1016118973493576</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02409357950091362</v>
+        <v>0.08817653357982635</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.05473070591688156</v>
+        <v>0.1502058804035187</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.03216205164790154</v>
+        <v>0.09588722139596939</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.02413243800401688</v>
+        <v>0.0092631746083498</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.03487608954310417</v>
+        <v>0.09636723250150681</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.00972035713493824</v>
+        <v>0.0178288072347641</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.03278931230306625</v>
+        <v>0.2943629324436188</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.06004271656274796</v>
+        <v>0.01870729401707649</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.05406949669122696</v>
+        <v>0.252820611000061</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.009165075607597828</v>
+        <v>0.1877405494451523</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0479234978556633</v>
+        <v>0.1304734349250793</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.03543504327535629</v>
+        <v>0.1223405376076698</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.04141245782375336</v>
+        <v>0.3511893749237061</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0285356342792511</v>
+        <v>0.01601526513695717</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01371928863227367</v>
+        <v>0.4217522740364075</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.08992103487253189</v>
+        <v>0.7452857494354248</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.04224938154220581</v>
+        <v>0.1741393357515335</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.09688316285610199</v>
+        <v>0.4489535689353943</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0724637359380722</v>
+        <v>0.1003909856081009</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.003599477000534534</v>
+        <v>0.2351135313510895</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.02626558393239975</v>
+        <v>0.1695748120546341</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.01732093468308449</v>
+        <v>0.05000638589262962</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.006335332058370113</v>
+        <v>0.1176447793841362</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.08346714824438095</v>
+        <v>0.1554223299026489</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01610144972801208</v>
+        <v>0.1078816205263138</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.02075017429888248</v>
+        <v>0.06883079558610916</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.006805709097534418</v>
+        <v>0.3521277904510498</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.04067938029766083</v>
+        <v>0.1281957626342773</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.03074569627642632</v>
+        <v>0.1676123440265656</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.2242997139692307</v>
+        <v>0.1120707988739014</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.01249695383012295</v>
+        <v>0.02992241829633713</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.04457202181220055</v>
+        <v>0.1366100907325745</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.01554986089468002</v>
+        <v>2.251907426398247e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07014036923646927</v>
+        <v>0.0001453703735023737</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00990816205739975</v>
+        <v>9.763858543010429e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02057818695902824</v>
+        <v>4.815342981601134e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04239463806152344</v>
+        <v>4.238596739014611e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002097753109410405</v>
+        <v>4.419248216436245e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01067756116390228</v>
+        <v>4.499032002058811e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001380008179694414</v>
+        <v>2.802296330628451e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001712454832158983</v>
+        <v>3.111548721790314e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00850962195545435</v>
+        <v>1.219607111124787e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05022390931844711</v>
+        <v>0.0001791459653759375</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006871121935546398</v>
+        <v>4.261820322426502e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02548253163695335</v>
+        <v>0.0001020718409563415</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04197346791625023</v>
+        <v>0.000112703513877932</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0110950693488121</v>
+        <v>5.053013956057839e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001232702750712633</v>
+        <v>2.370816946495324e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02883544191718102</v>
+        <v>3.226052649552003e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.003123383270576596</v>
+        <v>2.650531314429827e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00148590502794832</v>
+        <v>1.114157839765539e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02482464909553528</v>
+        <v>5.159576176083647e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>2.814098843373358e-05</v>
+        <v>1.465209334128303e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002084101084619761</v>
+        <v>3.280886812717654e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009272863157093525</v>
+        <v>4.024996087537147e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01045862771570683</v>
+        <v>7.862802704039495e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01056931260973215</v>
+        <v>1.180291292257607e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001095861662179232</v>
+        <v>1.659036570345052e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.006463431287556887</v>
+        <v>1.722129309200682e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.008662862703204155</v>
+        <v>1.340801190963248e-06</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01861467026174068</v>
+        <v>8.486075785185676e-06</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006873979233205318</v>
+        <v>1.559671909490135e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.009312724694609642</v>
+        <v>6.534085696330294e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01231355778872967</v>
+        <v>8.451545727439225e-05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.001865212805569172</v>
+        <v>5.783221240562852e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.01632852852344513</v>
+        <v>3.349513463035692e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.00452168844640255</v>
+        <v>4.58372087450698e-05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001410966156981885</v>
+        <v>4.608927611116087e-06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0117957815527916</v>
+        <v>3.592417442632723e-06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01724098064005375</v>
+        <v>4.538830035016872e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.004012210294604301</v>
+        <v>3.165808948324411e-07</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.005322746932506561</v>
+        <v>6.313201993179973e-06</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.003512540832161903</v>
+        <v>2.217844667029567e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003411879297345877</v>
+        <v>7.898962394392584e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.003405584255233407</v>
+        <v>1.92197894648416e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.002190755913034081</v>
+        <v>1.997319486690685e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.005157936364412308</v>
+        <v>1.058393354469445e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01791307888925076</v>
+        <v>3.884133548126556e-08</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.07147007435560226</v>
+        <v>0.0001910550781758502</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.005724911112338305</v>
+        <v>6.960315658943728e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003587245708331466</v>
+        <v>5.727473762817681e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.005477622617036104</v>
+        <v>0.0001097502608899958</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.002690784633159637</v>
+        <v>1.583048288011923e-05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001112047233618796</v>
+        <v>5.755948222940788e-06</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0114130349829793</v>
+        <v>1.83839238161454e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.206547888927162e-05</v>
+        <v>1.666718708293047e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.00731323566287756</v>
+        <v>2.989083623106126e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.009170481003820896</v>
+        <v>4.208840618957765e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.01075813453644514</v>
+        <v>1.256233190360945e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.00681858416646719</v>
+        <v>3.903676770278253e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.02529018931090832</v>
+        <v>4.595869540935382e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.01164405886083841</v>
+        <v>1.065482047124533e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.005726491566747427</v>
+        <v>1.986172537726816e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.02062829956412315</v>
+        <v>2.549268901930191e-05</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.004002900328487158</v>
+        <v>1.275307295145467e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.009336965158581734</v>
+        <v>2.129107815562747e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.02243887446820736</v>
+        <v>2.44660895987181e-05</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.003151390934363008</v>
+        <v>3.478400685708039e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.02280834503471851</v>
+        <v>3.499414560792502e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02214523404836655</v>
+        <v>2.421798853902146e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01527787279337645</v>
+        <v>2.249263161502313e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.000123028177767992</v>
+        <v>4.695173629443161e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.007544208317995071</v>
+        <v>1.155647441919427e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.00286469329148531</v>
+        <v>1.742898348311428e-06</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.00950933713465929</v>
+        <v>3.708559961523861e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04013717547059059</v>
+        <v>0.0001285487232962623</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01229055784642696</v>
+        <v>5.614007022813894e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002165388781577349</v>
+        <v>3.9200243918458e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.002201937139034271</v>
+        <v>4.325605186750181e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.008176990784704685</v>
+        <v>1.517185773991514e-05</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0166260227560997</v>
+        <v>2.977258918690495e-05</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.007690258324146271</v>
+        <v>8.127902219712269e-06</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.003632539650425315</v>
+        <v>3.118239419563906e-06</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0009689830476418138</v>
+        <v>6.185530310176546e-07</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0124470517039299</v>
+        <v>4.281608926248737e-05</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001853102876339108</v>
+        <v>7.935266694403253e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.009941259399056435</v>
+        <v>2.682226295291912e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.004262890666723251</v>
+        <v>2.167522325180471e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.00498903077095747</v>
+        <v>1.495665856054984e-05</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001050698570907116</v>
+        <v>4.041323336423375e-06</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001968028082046658</v>
+        <v>2.781481953206821e-06</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.004704682622104883</v>
+        <v>3.308987515993067e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02770276740193367</v>
+        <v>3.781196210184135e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02489689365029335</v>
+        <v>8.357129263458773e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0006756768561899662</v>
+        <v>1.560186319693457e-05</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.008321085013449192</v>
+        <v>5.030242027714849e-05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0270823035389185</v>
+        <v>0.0001130914024543017</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.003042312804609537</v>
+        <v>9.348143066745251e-06</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.002446394180878997</v>
+        <v>1.701785004115663e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.005624583456665277</v>
+        <v>2.103822407661937e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0008474006317555904</v>
+        <v>8.919411811803002e-06</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0004391064867377281</v>
+        <v>1.251545563718537e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.009305836632847786</v>
+        <v>4.081064253114164e-05</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002692129462957382</v>
+        <v>9.289801710110623e-06</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01411662809550762</v>
+        <v>5.848695764143486e-06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.002311107935383916</v>
+        <v>1.655589949223213e-05</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.006282894872128963</v>
+        <v>1.246943611477036e-05</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0004940289072692394</v>
+        <v>1.387313659506617e-06</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.003056678222492337</v>
+        <v>1.00155148174963e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.002491939347237349</v>
+        <v>4.388642082631122e-06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.02101856470108032</v>
+        <v>4.298018393456005e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.03990837559103966</v>
+        <v>1.185162909678183e-05</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.003059873823076487</v>
+        <v>1.162770786322653e-07</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03410201892256737</v>
+        <v>4.541692760540172e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01159583125263453</v>
+        <v>2.06343102036044e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002051133429631591</v>
+        <v>2.091446003760211e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.04074326902627945</v>
+        <v>6.286757525231224e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01250117458403111</v>
+        <v>7.708249540883116e-06</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.004076436161994934</v>
+        <v>6.789487088099122e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01374116912484169</v>
+        <v>2.007056536967866e-06</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01309563964605331</v>
+        <v>2.398384822299704e-05</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.003933674190193415</v>
+        <v>7.490646567021031e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.001396221457980573</v>
+        <v>2.246590884169564e-05</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01383760198950768</v>
+        <v>2.246463918709196e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.008790909312665462</v>
+        <v>2.77786202786956e-05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.003991243429481983</v>
+        <v>1.816729673009831e-05</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.004748451057821512</v>
+        <v>1.659447480051313e-05</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.006044522393494844</v>
+        <v>3.07026130030863e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.003851134330034256</v>
+        <v>2.079445584968198e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.003935130778700113</v>
+        <v>4.342978718341328e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.008078459650278091</v>
+        <v>6.313996436801972e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01526822056621313</v>
+        <v>3.907749942300143e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01313319336622953</v>
+        <v>6.265655974857509e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00144685769919306</v>
+        <v>2.621085513965227e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.009284209460020065</v>
+        <v>1.561285898787901e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0003104851930402219</v>
+        <v>9.471297744312324e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.003129132557660341</v>
+        <v>7.402418304991443e-06</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.008979173377156258</v>
+        <v>7.827316949260421e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>2.007824514294043e-05</v>
+        <v>8.170742148649879e-06</v>
       </c>
       <c r="EH10" t="n">
-        <v>6.68869906803593e-05</v>
+        <v>5.771150426880922e-06</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02280188351869583</v>
+        <v>1.354193045699503e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01304988097399473</v>
+        <v>1.131525823439006e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.004745736718177795</v>
+        <v>1.240904748556204e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.004542926326394081</v>
+        <v>9.136303560808301e-06</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.002107461215928197</v>
+        <v>3.267266947659664e-06</v>
       </c>
       <c r="EN10" t="n">
-        <v>3.53704672306776e-05</v>
+        <v>2.345723032703972e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.009966103360056877</v>
+        <v>1.132233410316985e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.003866207785904408</v>
+        <v>9.781830158317462e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01256202720105648</v>
+        <v>2.775795564957662e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01191132795065641</v>
+        <v>5.032492481404915e-06</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001274274429306388</v>
+        <v>2.772267544060014e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.008907058276236057</v>
+        <v>9.991062142944429e-06</v>
       </c>
       <c r="EU10" t="n">
-        <v>2.395396586507559e-05</v>
+        <v>1.412388428434497e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.006601540837436914</v>
+        <v>1.189776048704516e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.004005837254226208</v>
+        <v>1.565841921546962e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0007331091910600662</v>
+        <v>3.842874320980627e-06</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.007187142968177795</v>
+        <v>4.622028427547775e-05</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001204623724333942</v>
+        <v>5.630597570416285e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01120935752987862</v>
+        <v>6.128119821369182e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001111085526645184</v>
+        <v>1.235505442309659e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.005561096593737602</v>
+        <v>1.162059470516397e-05</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.002673451323062181</v>
+        <v>4.84272959511145e-06</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001448634313419461</v>
+        <v>6.878368822071934e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.003679746063426137</v>
+        <v>1.192873423860874e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.01061735395342112</v>
+        <v>2.050078728643712e-05</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.01673528552055359</v>
+        <v>1.401533336320426e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.009411588311195374</v>
+        <v>2.758849177553202e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.003606434678658843</v>
+        <v>3.103678682236932e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.005480068270117044</v>
+        <v>3.712618854478933e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.003711296012625098</v>
+        <v>9.117447916651145e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.002236240776255727</v>
+        <v>1.934083957166877e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.001674933591857553</v>
+        <v>3.213651507394388e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.001081352005712688</v>
+        <v>3.253828253946267e-06</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.005856226198375225</v>
+        <v>1.779743251972832e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001486103748902678</v>
+        <v>6.823094736319035e-05</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.007067886646836996</v>
+        <v>2.493509600753896e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.02562012895941734</v>
+        <v>3.299889795016497e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.01294733304530382</v>
+        <v>8.797578630037606e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.004354092758148909</v>
+        <v>4.448775143828243e-06</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0009708848083391786</v>
+        <v>9.163028153125197e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.02096831798553467</v>
+        <v>4.259821253072005e-06</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.002535826992243528</v>
+        <v>1.425381924491376e-05</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.005712715908885002</v>
+        <v>1.789177622413263e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.01935379952192307</v>
+        <v>2.685356776055414e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0120299244299531</v>
+        <v>2.466829027980566e-05</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.01084455661475658</v>
+        <v>2.148956991732121e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.004121070727705956</v>
+        <v>2.993250745930709e-05</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0124049223959446</v>
+        <v>4.838080258195987e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02001896873116493</v>
+        <v>1.789415182429366e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01758640632033348</v>
+        <v>1.301263910136186e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0006765954894945025</v>
+        <v>3.43402780345059e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03218394890427589</v>
+        <v>0.02323138527572155</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2123985588550568</v>
+        <v>0.03106526657938957</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001970803714357316</v>
+        <v>0.007582566235214472</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05954695492982864</v>
+        <v>0.0009203427471220493</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02524762973189354</v>
+        <v>0.008050419390201569</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03512627258896828</v>
+        <v>0.0008134954841807485</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01569333486258984</v>
+        <v>0.002421096665784717</v>
       </c>
       <c r="H11" t="n">
-        <v>0.006874158512800932</v>
+        <v>0.003787415567785501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03799623996019363</v>
+        <v>0.008267098106443882</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04798310995101929</v>
+        <v>0.02296377904713154</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1551417857408524</v>
+        <v>0.04188401252031326</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000998667674139142</v>
+        <v>0.00830546859651804</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04970483481884003</v>
+        <v>0.005047674290835857</v>
       </c>
       <c r="N11" t="n">
-        <v>0.05197658762335777</v>
+        <v>0.01400737836956978</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0496181957423687</v>
+        <v>0.008458489552140236</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02153880521655083</v>
+        <v>0.00212637335062027</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01459823828190565</v>
+        <v>0.005610655527561903</v>
       </c>
       <c r="R11" t="n">
-        <v>0.04297695308923721</v>
+        <v>0.01457512285560369</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008007552474737167</v>
+        <v>0.00134125561453402</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04505261033773422</v>
+        <v>0.002084814244881272</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003305527381598949</v>
+        <v>0.001017354195937514</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0317438617348671</v>
+        <v>0.003452051198109984</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0118562038987875</v>
+        <v>0.001585369696840644</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03326409682631493</v>
+        <v>0.003316709771752357</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01038662437349558</v>
+        <v>0.0001823985367082059</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02983665093779564</v>
+        <v>0.007117354311048985</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01563754491508007</v>
+        <v>0.006153897847980261</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.005570209585130215</v>
+        <v>0.002816240303218365</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02365129627287388</v>
+        <v>0.003321904689073563</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.008226718753576279</v>
+        <v>0.002823949558660388</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.009622259996831417</v>
+        <v>0.005612788256257772</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03183324635028839</v>
+        <v>0.007341057527810335</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.04511312395334244</v>
+        <v>0.0006677817436866462</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01111134327948093</v>
+        <v>0.002583344001322985</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.005103253293782473</v>
+        <v>0.003301578108221292</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01390464045107365</v>
+        <v>0.001298816874623299</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02250746451318264</v>
+        <v>0.005155757535248995</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0423847995698452</v>
+        <v>0.009551210328936577</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.005781557876616716</v>
+        <v>0.004804655443876982</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0195271410048008</v>
+        <v>0.005566958338022232</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.00570294726639986</v>
+        <v>0.00153848621994257</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02020914852619171</v>
+        <v>0.0007018429460003972</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01106815133243799</v>
+        <v>0.003922357689589262</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.008861131966114044</v>
+        <v>0.004774117842316628</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0199778713285923</v>
+        <v>0.0006646037800237536</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.004278106149286032</v>
+        <v>0.00924577284604311</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1301725804805756</v>
+        <v>0.02477611042559147</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0126482043415308</v>
+        <v>0.003785140113905072</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0162052046507597</v>
+        <v>0.003789097303524613</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01565140672028065</v>
+        <v>0.004836753942072392</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02215870469808578</v>
+        <v>0.004839300643652678</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.009280575439333916</v>
+        <v>9.378010872751474e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.01163647882640362</v>
+        <v>0.0001881578064057976</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.004251575563102961</v>
+        <v>0.001327602891251445</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.004964271560311317</v>
+        <v>0.005291454493999481</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02988169528543949</v>
+        <v>8.505117148160934e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01530836336314678</v>
+        <v>0.007553842384368181</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.00561278872191906</v>
+        <v>0.0003223868552595377</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.04413518309593201</v>
+        <v>0.007040021475404501</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.006751604378223419</v>
+        <v>0.007480467204004526</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.02079491317272186</v>
+        <v>0.001501751248724759</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.01403764449059963</v>
+        <v>0.002470530569553375</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.03011903539299965</v>
+        <v>0.005897273309528828</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.005082030780613422</v>
+        <v>0.003068313235417008</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.009723127819597721</v>
+        <v>0.004047286696732044</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0007646736921742558</v>
+        <v>0.001185010885819793</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01137683913111687</v>
+        <v>0.0002086812164634466</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02862579561769962</v>
+        <v>0.003717484883964062</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02628187462687492</v>
+        <v>0.0003823278821073472</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.004092734772711992</v>
+        <v>0.007748704869300127</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.01555137615650892</v>
+        <v>0.0007860062178224325</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.02620325796306133</v>
+        <v>0.001145778805948794</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.008584808558225632</v>
+        <v>0.002582892775535583</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.09379476308822632</v>
+        <v>0.02118542790412903</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01747508719563484</v>
+        <v>0.0009635635651648045</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.03247115015983582</v>
+        <v>0.003376293927431107</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0002523130387999117</v>
+        <v>0.0006189525010995567</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.005798126105219126</v>
+        <v>0.0003257656644564122</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.005874317139387131</v>
+        <v>0.004649373702704906</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01662790030241013</v>
+        <v>0.001401938730850816</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0148118007928133</v>
+        <v>0.006247374229133129</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.006990291178226471</v>
+        <v>0.006874875631183386</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.03027556091547012</v>
+        <v>0.01066372636705637</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.009601371362805367</v>
+        <v>0.0008536549285054207</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.007003752049058676</v>
+        <v>0.0001353393890894949</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.003352616913616657</v>
+        <v>0.0007128308061510324</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.005071286112070084</v>
+        <v>0.003150101052597165</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.004557847045361996</v>
+        <v>0.001790367416106164</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.007511753588914871</v>
+        <v>0.001142250373959541</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.002126110950484872</v>
+        <v>0.001592735992744565</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.03517862781882286</v>
+        <v>0.001565249636769295</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0001045982935465872</v>
+        <v>0.0215699914842844</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0005648810183629394</v>
+        <v>0.0006125608924776316</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01469586230814457</v>
+        <v>0.004502804018557072</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.03851167485117912</v>
+        <v>0.0009307030122727156</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.009540685452520847</v>
+        <v>0.008029846474528313</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01921222545206547</v>
+        <v>0.002435321919620037</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01412814203649759</v>
+        <v>0.00649631442502141</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.01987939327955246</v>
+        <v>0.003349989419803023</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002924415282905102</v>
+        <v>0.006243014242500067</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03093443065881729</v>
+        <v>0.01058236043900251</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01211680565029383</v>
+        <v>0.0003793060313910246</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01166554074734449</v>
+        <v>0.0009819632396101952</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006839251145720482</v>
+        <v>0.001986000686883926</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01438329461961985</v>
+        <v>0.002393025206401944</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.007949544116854668</v>
+        <v>0.001061646384187043</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.008233269676566124</v>
+        <v>6.125502113718539e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0006985227228142321</v>
+        <v>0.003012808272615075</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.007390893995761871</v>
+        <v>0.006004069931805134</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.05704014748334885</v>
+        <v>0.0131382942199707</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.003267480526119471</v>
+        <v>0.001019620918668807</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.04997266083955765</v>
+        <v>0.005083571188151836</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01462891697883606</v>
+        <v>0.009837613441050053</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.05554273352026939</v>
+        <v>0.01036885846406221</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.006689688190817833</v>
+        <v>0.00137878826353699</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.003066974226385355</v>
+        <v>0.0004141924437135458</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02291912958025932</v>
+        <v>0.007270412519574165</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.002414398826658726</v>
+        <v>0.002298285951837897</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.01245310250669718</v>
+        <v>0.005460497923195362</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.008721371181309223</v>
+        <v>0.005667869932949543</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.01683135703206062</v>
+        <v>0.001561541808769107</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02938702329993248</v>
+        <v>0.001176290214061737</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0009559514001011848</v>
+        <v>0.006411934737116098</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.003237128723412752</v>
+        <v>0.002600152511149645</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.002128139371052384</v>
+        <v>0.007320153061300516</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.02938557229936123</v>
+        <v>0.001462777727283537</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0007430021651089191</v>
+        <v>0.004600032698363066</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02029922604560852</v>
+        <v>0.003903945442289114</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01836094446480274</v>
+        <v>0.003959448542445898</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.005971289705485106</v>
+        <v>0.00274668144993484</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01777126267552376</v>
+        <v>0.007470551878213882</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0105474665760994</v>
+        <v>0.01064404752105474</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.002655174350365996</v>
+        <v>0.005037633236497641</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.00828669685870409</v>
+        <v>0.006633085664361715</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01359535846859217</v>
+        <v>0.006376803386956453</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.004175784531980753</v>
+        <v>0.005612928420305252</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01122288499027491</v>
+        <v>0.003924229182302952</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.005535811651498079</v>
+        <v>0.002565782517194748</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.01530192419886589</v>
+        <v>0.0002109618944814429</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004639754071831703</v>
+        <v>0.002631415845826268</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01953521743416786</v>
+        <v>0.002889480441808701</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.009476855397224426</v>
+        <v>0.001090939738787711</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001448547118343413</v>
+        <v>0.002398029202595353</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.004886786919087172</v>
+        <v>0.0002358936471864581</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.005899435840547085</v>
+        <v>0.003322256729006767</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01230136398226023</v>
+        <v>0.006307882722467184</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01422932930290699</v>
+        <v>0.004164428450167179</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.007742155343294144</v>
+        <v>0.003981264773756266</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0003305267891846597</v>
+        <v>0.001130955992266536</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03581495955586433</v>
+        <v>0.005263091530650854</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.01025629974901676</v>
+        <v>0.002478501293808222</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.03202563896775246</v>
+        <v>0.00159291853196919</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.004500781651586294</v>
+        <v>0.008218028582632542</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.002578237559646368</v>
+        <v>0.007028485182672739</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.03110994771122932</v>
+        <v>0.01251136511564255</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.007245442364364862</v>
+        <v>0.00148977036587894</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.01311893574893475</v>
+        <v>0.0002581320004537702</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.009864292107522488</v>
+        <v>0.001875080401077867</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01029846724122763</v>
+        <v>0.002466772217303514</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.005644898395985365</v>
+        <v>0.001292719505727291</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.00226086238399148</v>
+        <v>0.0002040871186181903</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.00441076373681426</v>
+        <v>0.003194173565134406</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.002659345045685768</v>
+        <v>0.002418313408270478</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.02028720080852509</v>
+        <v>0.007780455052852631</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0142994225025177</v>
+        <v>0.005703032948076725</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01370341330766678</v>
+        <v>0.004478859715163708</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.006421097554266453</v>
+        <v>0.003203149419277906</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.00363954296335578</v>
+        <v>0.0003121391637250781</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.009028831496834755</v>
+        <v>0.004678389523178339</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.006373318377882242</v>
+        <v>0.003945471718907356</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.006435250863432884</v>
+        <v>0.008788740262389183</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01125794183462858</v>
+        <v>0.0001433438155800104</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04275926202535629</v>
+        <v>0.003550442401319742</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.01428592298179865</v>
+        <v>0.005375315435230732</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02745112404227257</v>
+        <v>0.003276192815974355</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.001395493512973189</v>
+        <v>0.0062556485645473</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.005034955684095621</v>
+        <v>0.0010020995978266</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.02463188394904137</v>
+        <v>0.003927135374397039</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.01083041727542877</v>
+        <v>0.01221633888781071</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01619871705770493</v>
+        <v>0.005207010544836521</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.02591996267437935</v>
+        <v>0.003787151537835598</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.002360637299716473</v>
+        <v>0.003066602628678083</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.003802358405664563</v>
+        <v>0.003538505639880896</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.009078925475478172</v>
+        <v>0.005513049196451902</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.07337432354688644</v>
+        <v>0.003034900408238173</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.03178423643112183</v>
+        <v>0.0004882480134256184</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.07348792999982834</v>
+        <v>0.0005941636627539992</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.004643549211323261</v>
+        <v>0.004664235282689333</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.01076110545545816</v>
+        <v>0.01148184016346931</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.009669339284300804</v>
+        <v>0.0003039823786821216</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07197524607181549</v>
+        <v>0.002157620154321194</v>
       </c>
       <c r="C12" t="n">
-        <v>0.007208586670458317</v>
+        <v>0.0004427520907483995</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01128796301782131</v>
+        <v>0.0007143054390326142</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01458880119025707</v>
+        <v>0.001237671356648207</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00639175483956933</v>
+        <v>0.000325841479934752</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03572084009647369</v>
+        <v>0.0008943143184296787</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003638547845184803</v>
+        <v>0.0005387059645727277</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0005797703634016216</v>
+        <v>0.0005327616818249226</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01504797488451004</v>
+        <v>0.0002759706112556159</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05252392962574959</v>
+        <v>0.002822389360517263</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005199961364269257</v>
+        <v>8.47060582600534e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02402882464230061</v>
+        <v>0.001205075066536665</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01588805206120014</v>
+        <v>0.00117411301471293</v>
       </c>
       <c r="O12" t="n">
-        <v>0.009480693377554417</v>
+        <v>0.0005914032808504999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03020710870623589</v>
+        <v>0.001196901546791196</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01095870696008205</v>
+        <v>0.000615055556409061</v>
       </c>
       <c r="R12" t="n">
-        <v>0.004982705228030682</v>
+        <v>0.0001564949925523251</v>
       </c>
       <c r="S12" t="n">
-        <v>0.005066880024969578</v>
+        <v>0.0001320488954661414</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01756567880511284</v>
+        <v>0.0001089351062546484</v>
       </c>
       <c r="U12" t="n">
-        <v>0.006865448318421841</v>
+        <v>0.0003102290793322027</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001685940893366933</v>
+        <v>9.229508577845991e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>0.006230299826711416</v>
+        <v>0.0004006478702649474</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01105639711022377</v>
+        <v>0.0002938178367912769</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0009174102451652288</v>
+        <v>0.0001347926736343652</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.006776839960366488</v>
+        <v>3.086945798713714e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.008380349725484848</v>
+        <v>0.0001563443220220506</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.002480211202055216</v>
+        <v>0.0001750497176544741</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01078291609883308</v>
+        <v>9.057057468453422e-07</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.00347242271527648</v>
+        <v>0.0006369815673679113</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001871143467724323</v>
+        <v>0.0002037200465565547</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0101988110691309</v>
+        <v>0.0001407336676493287</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.007605582475662231</v>
+        <v>6.182202196214348e-05</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.001820549834519625</v>
+        <v>0.0001438200415577739</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.002633143682032824</v>
+        <v>0.0003784611471928656</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.007268025539815426</v>
+        <v>0.0002816715277731419</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01112830732017756</v>
+        <v>8.979623817140236e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01300337072461843</v>
+        <v>0.0007405400392599404</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002689098240807652</v>
+        <v>8.637505379738286e-05</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.006893530953675508</v>
+        <v>8.34611855680123e-05</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.003425454022362828</v>
+        <v>0.0004351946990936995</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0006701464881189167</v>
+        <v>0.000252564757829532</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.003569005290046334</v>
+        <v>4.615938087226823e-05</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.002421800745651126</v>
+        <v>0.0001636685337871313</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.005275605712085962</v>
+        <v>4.355404962552711e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.00879957340657711</v>
+        <v>0.0002469827886670828</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.05556334927678108</v>
+        <v>0.002113317139446735</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001364546827971935</v>
+        <v>0.0004464611411094666</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01097512152045965</v>
+        <v>0.0001742503081914037</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.006995928473770618</v>
+        <v>0.0001481490908190608</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.01119549106806517</v>
+        <v>0.000429287611041218</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01192539464682341</v>
+        <v>0.0001388275704812258</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.009154334664344788</v>
+        <v>0.0005145137547515333</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.004797652829438448</v>
+        <v>0.0001849451800808311</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.006779001094400883</v>
+        <v>7.870455738157034e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0100411968305707</v>
+        <v>0.0006915607955306768</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01277182996273041</v>
+        <v>0.000363523664418608</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.003569703549146652</v>
+        <v>0.0001360105961794034</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01828591339290142</v>
+        <v>0.0008478397503495216</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.00290707778185606</v>
+        <v>0.0004049884155392647</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.01179373078048229</v>
+        <v>0.000221030946704559</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.01101460959762335</v>
+        <v>9.64880600804463e-05</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.005616641137748957</v>
+        <v>0.0002693022252060473</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.002075487282127142</v>
+        <v>9.694592154119164e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.007020324934273958</v>
+        <v>0.0003066509962081909</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.002893333090469241</v>
+        <v>5.565561878029257e-06</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01388417184352875</v>
+        <v>0.0004734784306492656</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01529478188604116</v>
+        <v>0.000503252784255892</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.001743211061693728</v>
+        <v>0.0002978764241561294</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.002623022068291903</v>
+        <v>0.000245066185016185</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.007397426757961512</v>
+        <v>0.0002007486764341593</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.004066371358931065</v>
+        <v>0.0004491152067203075</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.004425994586199522</v>
+        <v>0.0003295076894573867</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.02841732837259769</v>
+        <v>0.001557456096634269</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.009682255797088146</v>
+        <v>6.090667739044875e-05</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.005857082083821297</v>
+        <v>0.0002448870800435543</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.001000773045234382</v>
+        <v>0.0003253172035329044</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.002027749549597502</v>
+        <v>0.0002574159298092127</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.001105086412280798</v>
+        <v>5.960655107628554e-05</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.008886148221790791</v>
+        <v>0.0003356835804879665</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.004224454052746296</v>
+        <v>0.0002281194756506011</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.003902621567249e-06</v>
+        <v>3.90287023037672e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.01251649763435125</v>
+        <v>0.0007026935345493257</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.005253682378679514</v>
+        <v>7.776597340125591e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.005947345402091742</v>
+        <v>0.0002978567499667406</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.000798103807028383</v>
+        <v>0.0001944567629834637</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.002148012397810817</v>
+        <v>0.0002524447627365589</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.007727762684226036</v>
+        <v>0.0001569617888890207</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0001690213539404795</v>
+        <v>0.0002010767784668133</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.005000404082238674</v>
+        <v>0.0003345074655953795</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.01655412279069424</v>
+        <v>0.0001671718200668693</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01002239715307951</v>
+        <v>0.001115569495595992</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.001393389422446489</v>
+        <v>8.30210919957608e-05</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.006662202998995781</v>
+        <v>0.0001699864806141704</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0168506633490324</v>
+        <v>0.0001477925397921354</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0002839574008248746</v>
+        <v>0.0005118366098031402</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.002694403054192662</v>
+        <v>0.0004340463201515377</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.002220313064754009</v>
+        <v>0.0002270207769470289</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0004665626911446452</v>
+        <v>0.0002033004711847752</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.001638761721551418</v>
+        <v>3.145133450743742e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.01208189129829407</v>
+        <v>0.0007711462094448507</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.005656515713781118</v>
+        <v>8.107534813461825e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01041226461529732</v>
+        <v>0.0002078296092804521</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001514348550699651</v>
+        <v>0.0001869286206783727</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002499691676348448</v>
+        <v>0.0002425810816930607</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.008736718446016312</v>
+        <v>0.0001919495116453618</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.001517163589596748</v>
+        <v>0.0002578346466179937</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.004203967284411192</v>
+        <v>0.0004034805751871318</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.005256431177258492</v>
+        <v>0.0003109137469436973</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.02442360483109951</v>
+        <v>0.0001300536969210953</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.003901492804288864</v>
+        <v>0.0004502953379414976</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01962215453386307</v>
+        <v>0.0001120253655244596</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.002254382474347949</v>
+        <v>0.0001926167460624129</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.002884042449295521</v>
+        <v>0.0004265870084054768</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.003330346196889877</v>
+        <v>3.534227289492264e-06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.004318314604461193</v>
+        <v>0.0006580242188647389</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.009062415920197964</v>
+        <v>9.172809222945943e-05</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0005669313250109553</v>
+        <v>6.225612014532089e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.004404284525662661</v>
+        <v>0.0002049318718491122</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.003846728475764394</v>
+        <v>6.614689482375979e-06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0002770876744762063</v>
+        <v>0.0004749644722323865</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0002259204775327817</v>
+        <v>4.143630940234289e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.007233637850731611</v>
+        <v>0.000507572025526315</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.009268053807318211</v>
+        <v>0.0004547392018139362</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.005006723571568727</v>
+        <v>0.0002518061664886773</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01132050529122353</v>
+        <v>0.0006494146073237062</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0001439880579710007</v>
+        <v>0.0001314254914177582</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.004810980521142483</v>
+        <v>0.0002776347391773015</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.008750510402023792</v>
+        <v>0.0001031097999657504</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.007555227261036634</v>
+        <v>0.0004221607523504645</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.006592143792659044</v>
+        <v>0.0003886565973516554</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.00797607097774744</v>
+        <v>0.0007830059621483088</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.001352623337879777</v>
+        <v>0.0001404397480655462</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.004179371986538172</v>
+        <v>0.0002828145516104996</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.001697277533821762</v>
+        <v>0.0002900506951846182</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.005872016772627831</v>
+        <v>7.950965664349496e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.003554567694664001</v>
+        <v>0.0008144049206748605</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.003123200731351972</v>
+        <v>0.0001671915670158342</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.009196072816848755</v>
+        <v>3.516318247420713e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0003655258624348789</v>
+        <v>0.0001425647496944293</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.003362789284437895</v>
+        <v>0.0001686887699179351</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.005923878867179155</v>
+        <v>6.718511576764286e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.001503650331869721</v>
+        <v>6.783747085137293e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.00204941350966692</v>
+        <v>0.0003305774298496544</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.004654800985008478</v>
+        <v>0.0001236035022884607</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.004486487712711096</v>
+        <v>0.0005172346718609333</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.00780307175591588</v>
+        <v>0.0001123563124565408</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.008400647900998592</v>
+        <v>0.0004031203570775688</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.007361708674579859</v>
+        <v>6.031319935573265e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.006642627529799938</v>
+        <v>0.00014082009147387</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.00795851182192564</v>
+        <v>1.086504562408663e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.006226672325283289</v>
+        <v>7.98229084466584e-05</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.009362535551190376</v>
+        <v>6.02577201789245e-05</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.001895721885375679</v>
+        <v>2.87526345346123e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.01123825088143349</v>
+        <v>0.0008405650150962174</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003436874831095338</v>
+        <v>9.480162407271564e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.007997914217412472</v>
+        <v>0.0001793300616554916</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003154310397803783</v>
+        <v>0.0001593073247931898</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.001462590647861362</v>
+        <v>0.0002472655032761395</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.01018988434225321</v>
+        <v>0.0001372989936498925</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.001390985795296729</v>
+        <v>0.0002651714021340013</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.005000175908207893</v>
+        <v>0.0003931177197955549</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.004867156501859426</v>
+        <v>0.000469689373858273</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01179278083145618</v>
+        <v>0.000295525387628004</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.008075185120105743</v>
+        <v>0.0004862427595071495</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.00203756894916296</v>
+        <v>0.0003327156882733107</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.004984760656952858</v>
+        <v>7.570635352749377e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0005848949076607823</v>
+        <v>0.0005785080720670521</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002052352298051119</v>
+        <v>3.128087337245233e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.005738188978284597</v>
+        <v>0.0004799879097845405</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.009769227355718613</v>
+        <v>0.0009665508987382054</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.006421963218599558</v>
+        <v>0.00035867840051651</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01212932541966438</v>
+        <v>0.00135860696900636</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.003591637592762709</v>
+        <v>0.000717224320396781</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01632042229175568</v>
+        <v>0.0006720760720781982</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.007776805199682713</v>
+        <v>0.0004474114102777094</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01544382702559233</v>
+        <v>0.0008847230346873403</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.005525989457964897</v>
+        <v>0.0003314415225759149</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.006826001219451427</v>
+        <v>0.0007695552776567638</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.006988033652305603</v>
+        <v>0.000528071541339159</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.01204719766974449</v>
+        <v>5.0034392188536e-05</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.006097020581364632</v>
+        <v>0.0006369313923642039</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0004247152828611434</v>
+        <v>0.0003782746207434684</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.006261010188609362</v>
+        <v>0.000299117062240839</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.01583071239292622</v>
+        <v>0.001163062872365117</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.006297079846262932</v>
+        <v>4.489484126679599e-07</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.02007991634309292</v>
+        <v>0.0001138834486482665</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.005366129800677299</v>
+        <v>1.067332959792111e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.006145531311631203</v>
+        <v>1.329242149950005e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02638169750571251</v>
+        <v>0.08843234926462173</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1381005495786667</v>
+        <v>0.2903520464897156</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02170850522816181</v>
+        <v>0.06461240351200104</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02795634418725967</v>
+        <v>0.01334440615028143</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04760324582457542</v>
+        <v>0.1141081973910332</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006263069342821836</v>
+        <v>0.159001424908638</v>
       </c>
       <c r="G13" t="n">
-        <v>0.028009083122015</v>
+        <v>0.04876236617565155</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01248601730912924</v>
+        <v>0.08649063855409622</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05048311501741409</v>
+        <v>0.03789591044187546</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03060773946344852</v>
+        <v>0.03272849693894386</v>
       </c>
       <c r="K13" t="n">
-        <v>0.106024332344532</v>
+        <v>0.3611272573471069</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01435147318989038</v>
+        <v>0.06374991685152054</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03666195273399353</v>
+        <v>0.09851792454719543</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06656590104103088</v>
+        <v>0.1680275350809097</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02295992150902748</v>
+        <v>0.1563556492328644</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01637142337858677</v>
+        <v>0.06584151834249496</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.006837945431470871</v>
+        <v>0.003305534832179546</v>
       </c>
       <c r="R13" t="n">
-        <v>0.04091234877705574</v>
+        <v>0.03100139833986759</v>
       </c>
       <c r="S13" t="n">
-        <v>0.003505364758893847</v>
+        <v>0.01363109424710274</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02793814614415169</v>
+        <v>0.05590901896357536</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01418139319866896</v>
+        <v>0.001894958782941103</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01398956030607224</v>
+        <v>0.08923794329166412</v>
       </c>
       <c r="W13" t="n">
-        <v>0.006541127804666758</v>
+        <v>0.05475817620754242</v>
       </c>
       <c r="X13" t="n">
-        <v>0.009869223460555077</v>
+        <v>0.04297704249620438</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01037963107228279</v>
+        <v>0.004257173277437687</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.001695226179435849</v>
+        <v>0.008947667665779591</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01084837131202221</v>
+        <v>0.03647695481777191</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02183464169502258</v>
+        <v>0.02441355586051941</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03316264227032661</v>
+        <v>0.03464153781533241</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01090404391288757</v>
+        <v>0.05839657783508301</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001627233810722828</v>
+        <v>0.05020738020539284</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01117252465337515</v>
+        <v>0.08121126890182495</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0173327811062336</v>
+        <v>0.07280495017766953</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.005927152931690216</v>
+        <v>0.009337777271866798</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01172339171171188</v>
+        <v>0.1333495676517487</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.002023837529122829</v>
+        <v>0.001071326201781631</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01147243566811085</v>
+        <v>0.00964859314262867</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01952119171619415</v>
+        <v>0.1143580973148346</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.01050399616360664</v>
+        <v>0.03407338261604309</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001567675732076168</v>
+        <v>0.03533897176384926</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.006391385104507208</v>
+        <v>0.07462622970342636</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01990148983895779</v>
+        <v>0.03992435708642006</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.009837944060564041</v>
+        <v>0.004227699246257544</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.006646727211773396</v>
+        <v>0.04553130269050598</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.006745255086570978</v>
+        <v>0.01064715068787336</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.005278685130178928</v>
+        <v>0.00489190686494112</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0931229293346405</v>
+        <v>0.3866130709648132</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0106997974216938</v>
+        <v>0.0123111829161644</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00439627468585968</v>
+        <v>0.01609981060028076</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.005013254471123219</v>
+        <v>0.06077448651194572</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.009014843963086605</v>
+        <v>0.1000592783093452</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02187421545386314</v>
+        <v>0.02623794972896576</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.01375751849263906</v>
+        <v>0.01774798892438412</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.005832364782691002</v>
+        <v>0.0110193807631731</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.01135450415313244</v>
+        <v>0.09128820151090622</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03308910876512527</v>
+        <v>0.09025002270936966</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01972637139260769</v>
+        <v>0.08219222724437714</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.00878443755209446</v>
+        <v>0.02770065143704414</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0510270968079567</v>
+        <v>0.09438832849264145</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01555666700005531</v>
+        <v>0.01325049344450235</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01099413260817528</v>
+        <v>0.0224272795021534</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.003944078925997019</v>
+        <v>0.02346275374293327</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0250767357647419</v>
+        <v>0.007505213376134634</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01674451865255833</v>
+        <v>0.01806183904409409</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.005608344450592995</v>
+        <v>0.04920945316553116</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.001372253987938166</v>
+        <v>0.00627099396660924</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02365433052182198</v>
+        <v>0.0541040375828743</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03543695062398911</v>
+        <v>0.04575621336698532</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02900507487356663</v>
+        <v>0.02425852231681347</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.00376034202054143</v>
+        <v>0.1318880468606949</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006075744517147541</v>
+        <v>0.02114641666412354</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.006027309689670801</v>
+        <v>0.00307477405294776</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.006107655353844166</v>
+        <v>0.02129774168133736</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05891247466206551</v>
+        <v>0.2506656646728516</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01863001100718975</v>
+        <v>0.02096496149897575</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.008730081841349602</v>
+        <v>0.1020420119166374</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0009706891141831875</v>
+        <v>0.0585862509906292</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.008724164217710495</v>
+        <v>0.06934698671102524</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007277193013578653</v>
+        <v>0.03220828622579575</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.01193704549223185</v>
+        <v>0.002266544383019209</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0121668791398406</v>
+        <v>0.03401569277048111</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001213258015923202</v>
+        <v>0.001127813942730427</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0262223593890667</v>
+        <v>0.1134069338440895</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0006281975074671209</v>
+        <v>0.02506553381681442</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.002317177364602685</v>
+        <v>0.003161621745675802</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0008515879744663835</v>
+        <v>0.01649558171629906</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.002435804344713688</v>
+        <v>0.03738494962453842</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.001259803306311369</v>
+        <v>0.02593204937875271</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.001125571085140109</v>
+        <v>0.006200449541211128</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01406137458980083</v>
+        <v>0.002496182452887297</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0375424437224865</v>
+        <v>0.06715165078639984</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.03812947869300842</v>
+        <v>0.1922687292098999</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001910649472847581</v>
+        <v>0.09781741350889206</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.00429565878584981</v>
+        <v>0.09197275340557098</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0007239821134135127</v>
+        <v>0.05155346542596817</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0004667090252041817</v>
+        <v>0.002817119937390089</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.02075593918561935</v>
+        <v>0.06826449930667877</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.03065007552504539</v>
+        <v>0.004361856728792191</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0005817064084112644</v>
+        <v>0.009768003597855568</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001411077566444874</v>
+        <v>0.02088038623332977</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.02317375689744949</v>
+        <v>0.1008135974407196</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.004101711791008711</v>
+        <v>0.0257654432207346</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.003279739757999778</v>
+        <v>0.01458789594471455</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.003003102261573076</v>
+        <v>0.01155791524797678</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.00183054618537426</v>
+        <v>0.03532824292778969</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001665211748331785</v>
+        <v>0.01074074395000935</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0007390970131382346</v>
+        <v>0.001878066686913371</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.009107289835810661</v>
+        <v>0.01193240284919739</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.003416450694203377</v>
+        <v>0.116784542798996</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.03391409292817116</v>
+        <v>0.06187624111771584</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.01469886023551226</v>
+        <v>0.004037691280245781</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.02375327609479427</v>
+        <v>0.1282217651605606</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.007962453179061413</v>
+        <v>0.005492636933922768</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.003450471209362149</v>
+        <v>0.09298396110534668</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02211124263703823</v>
+        <v>0.03867389261722565</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.003940454684197903</v>
+        <v>0.1055578738451004</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.008871002122759819</v>
+        <v>0.01464410126209259</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.002413520822301507</v>
+        <v>0.0005229203961789608</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.007504138629883528</v>
+        <v>0.0311884693801403</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.007612257264554501</v>
+        <v>0.021367147564888</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.007347287610173225</v>
+        <v>0.06518666446208954</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.002905009314417839</v>
+        <v>0.01741625741124153</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.004829124081879854</v>
+        <v>0.01201807521283627</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01815426163375378</v>
+        <v>0.00568711943924427</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.00515022361651063</v>
+        <v>0.04860223084688187</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.002322268672287464</v>
+        <v>0.02204685099422932</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.001184798311442137</v>
+        <v>0.02863839454948902</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01223612017929554</v>
+        <v>0.09076680243015289</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.000684474129229784</v>
+        <v>0.05029405653476715</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.305164187215269e-05</v>
+        <v>0.012517424300313</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.009605107828974724</v>
+        <v>0.09199071675539017</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.003113957587629557</v>
+        <v>0.07650047540664673</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.00399741530418396</v>
+        <v>0.01992849633097649</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.02333650179207325</v>
+        <v>0.07330633699893951</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.006719944998621941</v>
+        <v>0.05332403630018234</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.004128623753786087</v>
+        <v>0.02714146487414837</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01101913210004568</v>
+        <v>0.0219638142734766</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001321070827543736</v>
+        <v>0.0163249708712101</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01132386457175016</v>
+        <v>0.02048406563699245</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.008086150512099266</v>
+        <v>0.01776897348463535</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.003908899147063494</v>
+        <v>0.04457949101924896</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.01167917996644974</v>
+        <v>0.004351564683020115</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0003938049776479602</v>
+        <v>0.01022862363606691</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01743280701339245</v>
+        <v>0.007660411298274994</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.01209840551018715</v>
+        <v>0.001996561884880066</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0264244619756937</v>
+        <v>0.07616178691387177</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01263107545673847</v>
+        <v>0.05025208368897438</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.00496992189437151</v>
+        <v>0.03853582963347435</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.002928606467321515</v>
+        <v>0.04435159265995026</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.003136508632451296</v>
+        <v>0.01448003388941288</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.006861296482384205</v>
+        <v>0.02826939150691032</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.003606870770454407</v>
+        <v>0.03208256140351295</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.005860562436282635</v>
+        <v>0.0286607313901186</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002622977190185338</v>
+        <v>0.006063698790967464</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.02743009477853775</v>
+        <v>0.1256398558616638</v>
       </c>
       <c r="EZ13" t="n">
-        <v>9.215943282470107e-05</v>
+        <v>0.02674368768930435</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.001770790317095816</v>
+        <v>0.01779945567250252</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003057426540181041</v>
+        <v>0.006291798315942287</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.005230897571891546</v>
+        <v>0.03995002433657646</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001191073097288609</v>
+        <v>0.02800252102315426</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.002831256482750177</v>
+        <v>0.002186496276408434</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.008041288703680038</v>
+        <v>0.01734969019889832</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0007863603532314301</v>
+        <v>0.0365954227745533</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0120293851941824</v>
+        <v>0.05931297317147255</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.009794740006327629</v>
+        <v>0.002596828155219555</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01015857420861721</v>
+        <v>0.06987936049699783</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.009985265322029591</v>
+        <v>0.03695173189043999</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0008652890101075172</v>
+        <v>0.01968766935169697</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.00597020611166954</v>
+        <v>0.01845169626176357</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.007539165671914816</v>
+        <v>0.06112337857484818</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01604060083627701</v>
+        <v>0.01218864414840937</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01360338553786278</v>
+        <v>0.08469104021787643</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01331809535622597</v>
+        <v>0.1175504177808762</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01180979888886213</v>
+        <v>0.01863805204629898</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.00297286082059145</v>
+        <v>0.02363517694175243</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01033383794128895</v>
+        <v>0.1097791120409966</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01068012230098248</v>
+        <v>0.02466550096869469</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.02002562209963799</v>
+        <v>0.01529748737812042</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.02476439066231251</v>
+        <v>0.02254838868975639</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01146345585584641</v>
+        <v>0.02387835644185543</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02097207494080067</v>
+        <v>0.01078004762530327</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01473355945199728</v>
+        <v>0.01730776205658913</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.008245114237070084</v>
+        <v>0.02912875078618526</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.009889477863907814</v>
+        <v>0.00685293460264802</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01878736168146133</v>
+        <v>0.04281814023852348</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02372186258435249</v>
+        <v>0.05358671396970749</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.02187224477529526</v>
+        <v>0.009233029559254646</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01612873189151287</v>
+        <v>0.04734225943684578</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.004625734873116016</v>
+        <v>0.03211415186524391</v>
       </c>
     </row>
     <row r="14">
@@ -8396,2278 +8396,2278 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.05087659507989883</v>
+        <v>0.2956071197986603</v>
       </c>
       <c r="B15" t="n">
-        <v>0.6551549434661865</v>
+        <v>0.2097222208976746</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5674992799758911</v>
+        <v>0.5267529487609863</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2443849295377731</v>
+        <v>0.6589598059654236</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7310421466827393</v>
+        <v>0.4009454846382141</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07958438992500305</v>
+        <v>0.06672003865242004</v>
       </c>
       <c r="G15" t="n">
-        <v>0.279327392578125</v>
+        <v>0.1810636818408966</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2367377281188965</v>
+        <v>0.0904914066195488</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3321493566036224</v>
+        <v>0.1263859272003174</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1313386261463165</v>
+        <v>0.270944356918335</v>
       </c>
       <c r="K15" t="n">
-        <v>0.466825544834137</v>
+        <v>0.4254042506217957</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3783947825431824</v>
+        <v>0.3758119940757751</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1917919367551804</v>
+        <v>0.5662096738815308</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8066661953926086</v>
+        <v>0.2903485298156738</v>
       </c>
       <c r="O15" t="n">
-        <v>0.126898393034935</v>
+        <v>0.1929424703121185</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2723886370658875</v>
+        <v>0.1990344524383545</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1594605892896652</v>
+        <v>0.0314088836312294</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2525058090686798</v>
+        <v>0.1766329705715179</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02855133265256882</v>
+        <v>0.1575530022382736</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1152994111180305</v>
+        <v>0.2959610819816589</v>
       </c>
       <c r="U15" t="n">
-        <v>0.007808821275830269</v>
+        <v>0.3718747198581696</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1589225828647614</v>
+        <v>0.1274172365665436</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1012454107403755</v>
+        <v>0.08791451901197433</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1490786224603653</v>
+        <v>0.1531151831150055</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004327455535531044</v>
+        <v>0.02875912562012672</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1286806166172028</v>
+        <v>0.1173782348632812</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.07079032808542252</v>
+        <v>0.1134361550211906</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.07417525351047516</v>
+        <v>0.2290864139795303</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1701214760541916</v>
+        <v>0.07470604032278061</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003837145864963531</v>
+        <v>0.3653550744056702</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1107606291770935</v>
+        <v>0.08105684816837311</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05915375798940659</v>
+        <v>0.04542502760887146</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1247408464550972</v>
+        <v>0.08229652047157288</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0136243924498558</v>
+        <v>0.02987766265869141</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.06574058532714844</v>
+        <v>0.2509883642196655</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02492513135075569</v>
+        <v>0.1377080976963043</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.006663396954536438</v>
+        <v>0.1465889811515808</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3569846749305725</v>
+        <v>0.475545346736908</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.004030823707580566</v>
+        <v>0.04238261282444</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.06992025673389435</v>
+        <v>0.06467325240373611</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.009083693847060204</v>
+        <v>0.4654800295829773</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1487974226474762</v>
+        <v>0.03846336528658867</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.02254658192396164</v>
+        <v>0.06266280263662338</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.03750970214605331</v>
+        <v>0.01202301494777203</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1108453348278999</v>
+        <v>0.04379170387983322</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.1803907006978989</v>
+        <v>0.1735562086105347</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5895699262619019</v>
+        <v>0.483345091342926</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3790908753871918</v>
+        <v>0.2867020666599274</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0575115866959095</v>
+        <v>0.4015323221683502</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1414304226636887</v>
+        <v>0.6068621873855591</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1834969967603683</v>
+        <v>0.1208071559667587</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.01015175879001617</v>
+        <v>0.04079088196158409</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.011645233258605</v>
+        <v>0.3381299376487732</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1124794781208038</v>
+        <v>0.1412918716669083</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0431271605193615</v>
+        <v>0.1455797255039215</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03053856641054153</v>
+        <v>0.8822528123855591</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.05798040330410004</v>
+        <v>0.5593940019607544</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.2798956632614136</v>
+        <v>0.03164126351475716</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.6100434064865112</v>
+        <v>1.397466778755188</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.03262158110737801</v>
+        <v>0.1293768137693405</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.1656705737113953</v>
+        <v>0.1529793739318848</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.07732705026865005</v>
+        <v>0.2975718080997467</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1641398519277573</v>
+        <v>0.09394967555999756</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.2245603054761887</v>
+        <v>0.1930830478668213</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.2150991857051849</v>
+        <v>0.02828101813793182</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.05522866547107697</v>
+        <v>0.1822481900453568</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0587795153260231</v>
+        <v>0.04017169401049614</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1237502098083496</v>
+        <v>0.1148371398448944</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1589523255825043</v>
+        <v>0.1279436051845551</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1490662693977356</v>
+        <v>0.06856667250394821</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.09714406728744507</v>
+        <v>0.03930354863405228</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.1061887145042419</v>
+        <v>0.1029217913746834</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.1371117234230042</v>
+        <v>0.2878467440605164</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3253659605979919</v>
+        <v>0.6190174221992493</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.3999916911125183</v>
+        <v>0.3027207553386688</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.005585707724094391</v>
+        <v>0.08227820694446564</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1146147325634956</v>
+        <v>0.1057926341891289</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.1014298796653748</v>
+        <v>0.2875040471553802</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0402594730257988</v>
+        <v>0.08272229135036469</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.03187799453735352</v>
+        <v>0.02126302942633629</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.009496085345745087</v>
+        <v>0.05293795466423035</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.005182996392250061</v>
+        <v>0.1782946437597275</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.09676089882850647</v>
+        <v>0.2129542529582977</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.07527307420969009</v>
+        <v>0.108192652463913</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.1311590522527695</v>
+        <v>0.1204595863819122</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.1575766354799271</v>
+        <v>0.07461127638816833</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.03721575811505318</v>
+        <v>5.357712507247925e-05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.001892564352601767</v>
+        <v>0.04361782968044281</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.06878098100423813</v>
+        <v>0.05271559953689575</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.07268635183572769</v>
+        <v>0.01039471291005611</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.1553008109331131</v>
+        <v>0.1754097938537598</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.1105695888400078</v>
+        <v>0.1493643224239349</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.02541904337704182</v>
+        <v>0.136192575097084</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.2425942271947861</v>
+        <v>0.3277369141578674</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.2039075642824173</v>
+        <v>0.7248969674110413</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.1053209602832794</v>
+        <v>0.2206081598997116</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.14927938580513</v>
+        <v>0.1120670214295387</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.06514639407396317</v>
+        <v>0.1484841108322144</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.05760979279875755</v>
+        <v>0.006742604076862335</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.02922976016998291</v>
+        <v>0.1385423690080643</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.02999508753418922</v>
+        <v>0.1613538563251495</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.06534281373023987</v>
+        <v>0.1130383536219597</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1060666590929031</v>
+        <v>0.07231292128562927</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.129588320851326</v>
+        <v>0.07916752994060516</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.05452645197510719</v>
+        <v>0.06770159304141998</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.006788872182369232</v>
+        <v>0.06051571667194366</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.03634814918041229</v>
+        <v>0.09207994490861893</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.127794086933136</v>
+        <v>0.0857095867395401</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1504220068454742</v>
+        <v>0.1791310012340546</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.05551958084106445</v>
+        <v>0.2234741747379303</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.1118040233850479</v>
+        <v>0.3577977120876312</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.313539445400238</v>
+        <v>0.1020399779081345</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.03317458182573318</v>
+        <v>0.02798650041222572</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.06216038390994072</v>
+        <v>0.5481149554252625</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.08455443382263184</v>
+        <v>0.07679139077663422</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1646832972764969</v>
+        <v>0.1235490888357162</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.1734495460987091</v>
+        <v>0.3839857280254364</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.09073086082935333</v>
+        <v>0.182063564658165</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03581081703305244</v>
+        <v>0.09976625442504883</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.04676191508769989</v>
+        <v>0.02990041300654411</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.1062984466552734</v>
+        <v>0.1913415789604187</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1561384946107864</v>
+        <v>0.1405749469995499</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1888758391141891</v>
+        <v>0.2122303247451782</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.02415505982935429</v>
+        <v>0.02964574843645096</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.03749634698033333</v>
+        <v>0.1021972745656967</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.04469552263617516</v>
+        <v>0.08621394634246826</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07998201251029968</v>
+        <v>0.08343725651502609</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.1005874872207642</v>
+        <v>0.3097074627876282</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.09500700235366821</v>
+        <v>0.03089131414890289</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.07233388721942902</v>
+        <v>0.2430682182312012</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.1225016638636589</v>
+        <v>0.5633408427238464</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.2058645933866501</v>
+        <v>0.0520835816860199</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01248658169060946</v>
+        <v>0.03888415545225143</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.07837804406881332</v>
+        <v>0.07272306829690933</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.01626089215278625</v>
+        <v>0.0886707529425621</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.03519788384437561</v>
+        <v>0.1450945734977722</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05209698528051376</v>
+        <v>0.01136776804924011</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.04099832475185394</v>
+        <v>0.01367053389549255</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05698300525546074</v>
+        <v>0.04062521085143089</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1936584562063217</v>
+        <v>0.005801025778055191</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.04288386553525925</v>
+        <v>0.01385165564715862</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.09687155485153198</v>
+        <v>0.03340959548950195</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.02353386580944061</v>
+        <v>0.1138632819056511</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.1337963044643402</v>
+        <v>0.141795352101326</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.05121636763215065</v>
+        <v>0.005607975646853447</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04193691909313202</v>
+        <v>0.2470362484455109</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0941179096698761</v>
+        <v>0.2668220698833466</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.1078903749585152</v>
+        <v>0.04933926835656166</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03584827482700348</v>
+        <v>0.07747944444417953</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.2015871703624725</v>
+        <v>0.0001887902617454529</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.08830837160348892</v>
+        <v>0.06691525876522064</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.1253560036420822</v>
+        <v>0.1440747678279877</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.2597638070583344</v>
+        <v>0.1134090796113014</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.006284326314926147</v>
+        <v>0.2064187526702881</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01666093617677689</v>
+        <v>0.1679784804582596</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.06052092090249062</v>
+        <v>0.0819430872797966</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1433342844247818</v>
+        <v>0.1260117292404175</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.1427036672830582</v>
+        <v>0.1086092814803123</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0803791880607605</v>
+        <v>0.09681946784257889</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.03324206918478012</v>
+        <v>0.0298017542809248</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.1015682891011238</v>
+        <v>0.09976047277450562</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.05603266134858131</v>
+        <v>0.05500089377164841</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.05391434580087662</v>
+        <v>0.06035315990447998</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.2170421779155731</v>
+        <v>0.2608437836170197</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1610262095928192</v>
+        <v>0.3459382355213165</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0692000687122345</v>
+        <v>0.002262741327285767</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1508391499519348</v>
+        <v>0.4723259210586548</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.008993562310934067</v>
+        <v>0.5071651339530945</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.156096339225769</v>
+        <v>0.007570497691631317</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.01165476627647877</v>
+        <v>0.1440925449132919</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.1292327493429184</v>
+        <v>0.232509583234787</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.008302941918373108</v>
+        <v>0.1867574751377106</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.1076796129345894</v>
+        <v>0.5298460125923157</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.2010010480880737</v>
+        <v>0.2371300458908081</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.3002151250839233</v>
+        <v>0.1869992017745972</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.03944172710180283</v>
+        <v>0.3470439612865448</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.02006193809211254</v>
+        <v>0.6564397811889648</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.1319470703601837</v>
+        <v>0.07823626697063446</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.2409802228212357</v>
+        <v>0.04030001908540726</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.01767439022660255</v>
+        <v>0.03745275735855103</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.1085974276065826</v>
+        <v>0.0450814962387085</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06191705912351608</v>
+        <v>0.1747282892465591</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.1324360966682434</v>
+        <v>0.1795162111520767</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.06201763823628426</v>
+        <v>0.2364161610603333</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.09203535318374634</v>
+        <v>0.00696660578250885</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.2361350208520889</v>
+        <v>0.3875554203987122</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.1564380675554276</v>
+        <v>0.02385037019848824</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.4043647348880768</v>
+        <v>0.1247090697288513</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.08564833551645279</v>
+        <v>0.09568849951028824</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0001171166441054083</v>
+        <v>6.450891669373959e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001237048185430467</v>
+        <v>0.03261193633079529</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001067018674802966</v>
+        <v>0.0148157374933362</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004314736288506538</v>
+        <v>0.009803183376789093</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003088231314904988</v>
+        <v>0.007461476139724255</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006134618306532502</v>
+        <v>0.02278399094939232</v>
       </c>
       <c r="G16" t="n">
-        <v>5.732083081966266e-05</v>
+        <v>0.006443632766604424</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003735339269042015</v>
+        <v>0.007353258784860373</v>
       </c>
       <c r="I16" t="n">
-        <v>6.168369509396143e-06</v>
+        <v>0.01509168464690447</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000218141358345747</v>
+        <v>0.002680992009118199</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001158298342488706</v>
+        <v>0.03197450190782547</v>
       </c>
       <c r="L16" t="n">
-        <v>1.446435453544836e-05</v>
+        <v>0.02154011465609074</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0002432382898405194</v>
+        <v>0.02694818004965782</v>
       </c>
       <c r="N16" t="n">
-        <v>1.148731826106086e-06</v>
+        <v>0.002372649498283863</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006787022575736046</v>
+        <v>0.0289232861250639</v>
       </c>
       <c r="P16" t="n">
-        <v>7.027263927739114e-05</v>
+        <v>0.00821941252797842</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001337644644081593</v>
+        <v>0.0007522674277424812</v>
       </c>
       <c r="R16" t="n">
-        <v>3.434595419093966e-05</v>
+        <v>0.01967684179544449</v>
       </c>
       <c r="S16" t="n">
-        <v>4.552691098069772e-05</v>
+        <v>0.005132936872541904</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001019271439872682</v>
+        <v>0.007159569300711155</v>
       </c>
       <c r="U16" t="n">
-        <v>6.771088374080136e-05</v>
+        <v>0.003238328266888857</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001876055321190506</v>
+        <v>0.001620011869817972</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001159649837063625</v>
+        <v>0.004558240994811058</v>
       </c>
       <c r="X16" t="n">
-        <v>6.212814696482383e-06</v>
+        <v>0.002088551176711917</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.402502832410391e-05</v>
+        <v>0.006049223244190216</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0001151540491264313</v>
+        <v>0.00212807534262538</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.298263618489727e-05</v>
+        <v>0.003804826410487294</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.940578658832237e-05</v>
+        <v>0.004214445129036903</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.087259988707956e-05</v>
+        <v>0.0008902432164177299</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.072104638908058e-05</v>
+        <v>0.007190936245024204</v>
       </c>
       <c r="AE16" t="n">
-        <v>9.967650839826092e-05</v>
+        <v>0.007986921817064285</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.171065903501585e-05</v>
+        <v>0.01047243736684322</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.97924325929489e-06</v>
+        <v>0.01429695636034012</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.886056452349294e-05</v>
+        <v>0.003449574811384082</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.00010916428436758</v>
+        <v>0.02384053356945515</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7.179049134720117e-05</v>
+        <v>0.0003467149799689651</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0002299183834111318</v>
+        <v>0.003320765215903521</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.248706581071019e-05</v>
+        <v>0.00529630109667778</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.746865382301621e-05</v>
+        <v>0.0006982332561165094</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.815226803766564e-06</v>
+        <v>0.002923974767327309</v>
       </c>
       <c r="AO16" t="n">
-        <v>6.595397280761972e-05</v>
+        <v>0.007218272890895605</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001731083902996033</v>
+        <v>0.002600452397018671</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.989786248188466e-05</v>
+        <v>0.0002487649326212704</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0001092257371055894</v>
+        <v>0.007076353300362825</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001408308889949694</v>
+        <v>0.002587185706943274</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.921795021393336e-05</v>
+        <v>0.005858135409653187</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.000686386541929096</v>
+        <v>0.03017770126461983</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0001776876015355811</v>
+        <v>0.009323012083768845</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.172630749759264e-05</v>
+        <v>0.009552048519253731</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0002155125694116578</v>
+        <v>0.02012882381677628</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0002793985768221319</v>
+        <v>0.02282928489148617</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.236093708546832e-05</v>
+        <v>0.002349377376958728</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0001498496276326478</v>
+        <v>0.008714592084288597</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0001002957942546345</v>
+        <v>0.002513691317290068</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.35571967298165e-05</v>
+        <v>0.005796131677925587</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.000255537626799196</v>
+        <v>0.00336635927669704</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0003351273480802774</v>
+        <v>0.01164150424301624</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.310872489237227e-05</v>
+        <v>0.00426699873059988</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.064659050432965e-05</v>
+        <v>0.01656481251120567</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0001000667907646857</v>
+        <v>0.003680491354316473</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001175436555058695</v>
+        <v>0.007365399040281773</v>
       </c>
       <c r="BJ16" t="n">
-        <v>5.158224666956812e-05</v>
+        <v>0.001961924834176898</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.267237090971321e-05</v>
+        <v>0.009988238103687763</v>
       </c>
       <c r="BL16" t="n">
-        <v>8.67922353791073e-05</v>
+        <v>0.0002412336179986596</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0001645397569518536</v>
+        <v>0.01067366451025009</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0001411358680343255</v>
+        <v>0.005735649261623621</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.725633723661304e-05</v>
+        <v>0.002897663973271847</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.047788388561457e-05</v>
+        <v>0.005562174133956432</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.611511419876479e-05</v>
+        <v>0.004375656135380268</v>
       </c>
       <c r="BR16" t="n">
-        <v>7.142277172533795e-05</v>
+        <v>0.004331436473876238</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.146472828229889e-05</v>
+        <v>0.001706309500150383</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0001771178212948143</v>
+        <v>0.0026514264754951</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.812959403148852e-05</v>
+        <v>0.002418969292193651</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0004195033689029515</v>
+        <v>0.01717999763786793</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0001338043803116307</v>
+        <v>0.004137756302952766</v>
       </c>
       <c r="BX16" t="n">
-        <v>1.615720975678414e-05</v>
+        <v>0.003528164932504296</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.103412594413385e-05</v>
+        <v>0.004085303284227848</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001687228505034</v>
+        <v>0.00911472924053669</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.878321356547531e-05</v>
+        <v>0.01079789269715548</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.570114080910571e-05</v>
+        <v>0.001182300271466374</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.579787855618633e-05</v>
+        <v>0.005691076628863811</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.315476326155476e-05</v>
+        <v>0.0002508106990717351</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0002360898215556517</v>
+        <v>0.01107136625796556</v>
       </c>
       <c r="CF16" t="n">
-        <v>9.1514055384323e-05</v>
+        <v>0.005064566619694233</v>
       </c>
       <c r="CG16" t="n">
-        <v>7.011259731370956e-05</v>
+        <v>0.003586011473089457</v>
       </c>
       <c r="CH16" t="n">
-        <v>5.832851456943899e-05</v>
+        <v>0.0006316102808341384</v>
       </c>
       <c r="CI16" t="n">
-        <v>4.306236587581225e-05</v>
+        <v>0.00453645084053278</v>
       </c>
       <c r="CJ16" t="n">
-        <v>6.251956074265763e-05</v>
+        <v>0.0002871012839023024</v>
       </c>
       <c r="CK16" t="n">
-        <v>8.669171074870974e-05</v>
+        <v>0.0006858757697045803</v>
       </c>
       <c r="CL16" t="n">
-        <v>6.106386717874557e-05</v>
+        <v>0.002086003310978413</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0002791569568216801</v>
+        <v>0.004805959761142731</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0001084002433344722</v>
+        <v>0.003412917722016573</v>
       </c>
       <c r="CO16" t="n">
-        <v>5.603586487268331e-06</v>
+        <v>0.009644506499171257</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0002151614025933668</v>
+        <v>0.0124169671908021</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0001465432142140344</v>
+        <v>0.005693668499588966</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0003277101495768875</v>
+        <v>0.002700289944186807</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0002248292585136369</v>
+        <v>0.006489779334515333</v>
       </c>
       <c r="CT16" t="n">
-        <v>6.952360126888379e-05</v>
+        <v>0.002155381953343749</v>
       </c>
       <c r="CU16" t="n">
-        <v>5.762340151704848e-05</v>
+        <v>0.006497327238321304</v>
       </c>
       <c r="CV16" t="n">
-        <v>3.773729258682579e-05</v>
+        <v>0.002491294406354427</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0002261948538944125</v>
+        <v>0.008660925552248955</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0001248415355803445</v>
+        <v>0.006778721697628498</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.000122028446639888</v>
+        <v>0.00521854730322957</v>
       </c>
       <c r="CZ16" t="n">
-        <v>5.122640504851006e-05</v>
+        <v>0.0007996554486453533</v>
       </c>
       <c r="DA16" t="n">
-        <v>6.338359526125714e-05</v>
+        <v>0.007722056936472654</v>
       </c>
       <c r="DB16" t="n">
-        <v>5.995520405122079e-05</v>
+        <v>0.001735553843900561</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0001494045718573034</v>
+        <v>0.0007644675788469613</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.021639663027599e-05</v>
+        <v>0.003057485911995173</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0001370056997984648</v>
+        <v>0.0008778998162597418</v>
       </c>
       <c r="DF16" t="n">
-        <v>6.6605512984097e-05</v>
+        <v>0.01817023567855358</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.331540822022362e-06</v>
+        <v>0.01512507721781731</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0004261558351572603</v>
+        <v>0.0001692943624220788</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0004867747484240681</v>
+        <v>0.005357318092137575</v>
       </c>
       <c r="DJ16" t="n">
-        <v>8.768583938945085e-05</v>
+        <v>0.01782485283911228</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0001551551395095885</v>
+        <v>0.005678699351847172</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0001668906043050811</v>
+        <v>0.009497806429862976</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0001775909477146342</v>
+        <v>0.0005609606159850955</v>
       </c>
       <c r="DN16" t="n">
-        <v>7.034532609395683e-05</v>
+        <v>0.002195702865719795</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0001335168199148029</v>
+        <v>0.008114300668239594</v>
       </c>
       <c r="DP16" t="n">
-        <v>8.827017154544592e-05</v>
+        <v>0.004048534668982029</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001425681984983385</v>
+        <v>0.008565829135477543</v>
       </c>
       <c r="DR16" t="n">
-        <v>4.019356128992513e-05</v>
+        <v>0.0001300816657021642</v>
       </c>
       <c r="DS16" t="n">
-        <v>9.399465488968417e-05</v>
+        <v>0.004869308788329363</v>
       </c>
       <c r="DT16" t="n">
-        <v>5.445639544632286e-05</v>
+        <v>0.002665768377482891</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0001296676200581715</v>
+        <v>0.01015174202620983</v>
       </c>
       <c r="DV16" t="n">
-        <v>5.699021494365297e-05</v>
+        <v>0.004803964402526617</v>
       </c>
       <c r="DW16" t="n">
-        <v>3.70309135178104e-06</v>
+        <v>0.0006172927096486092</v>
       </c>
       <c r="DX16" t="n">
-        <v>5.746578608523123e-05</v>
+        <v>0.008592592552304268</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001308555947616696</v>
+        <v>0.01233669370412827</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.62122048297897e-05</v>
+        <v>0.002585174050182104</v>
       </c>
       <c r="EA16" t="n">
-        <v>7.160037057474256e-05</v>
+        <v>0.007061610464006662</v>
       </c>
       <c r="EB16" t="n">
-        <v>4.216229353914969e-05</v>
+        <v>0.003841590136289597</v>
       </c>
       <c r="EC16" t="n">
-        <v>9.528168448014185e-05</v>
+        <v>0.012037243694067</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.266719457111321e-05</v>
+        <v>0.005447434261441231</v>
       </c>
       <c r="EE16" t="n">
-        <v>8.482078555971384e-05</v>
+        <v>0.01784889400005341</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0002097113756462932</v>
+        <v>0.000280670530628413</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0002718578616622835</v>
+        <v>0.001828609616495669</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0001542687678011134</v>
+        <v>0.0006986712105572224</v>
       </c>
       <c r="EI16" t="n">
-        <v>7.639691466465592e-05</v>
+        <v>0.01022890489548445</v>
       </c>
       <c r="EJ16" t="n">
-        <v>6.392368231900036e-05</v>
+        <v>0.0005076772067695856</v>
       </c>
       <c r="EK16" t="n">
-        <v>5.531381611945108e-05</v>
+        <v>0.0009288747096434236</v>
       </c>
       <c r="EL16" t="n">
-        <v>4.676752723753452e-05</v>
+        <v>0.0029989427421242</v>
       </c>
       <c r="EM16" t="n">
-        <v>3.519750316627324e-05</v>
+        <v>0.003488517832010984</v>
       </c>
       <c r="EN16" t="n">
-        <v>1.894168417493347e-05</v>
+        <v>0.01030332408845425</v>
       </c>
       <c r="EO16" t="n">
-        <v>4.368257577880286e-05</v>
+        <v>0.002965949941426516</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0001042201110976748</v>
+        <v>0.008361048996448517</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0001334457192569971</v>
+        <v>0.002655017655342817</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0001554163900436834</v>
+        <v>0.005249736830592155</v>
       </c>
       <c r="ES16" t="n">
-        <v>6.048800423741341e-05</v>
+        <v>0.006754779256880283</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0001966887502931058</v>
+        <v>0.009398192167282104</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0001422098866896704</v>
+        <v>0.002194348722696304</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0002619430888444185</v>
+        <v>0.000391942507121712</v>
       </c>
       <c r="EW16" t="n">
-        <v>5.336994217941537e-05</v>
+        <v>0.001917108776979148</v>
       </c>
       <c r="EX16" t="n">
-        <v>5.828135181218386e-05</v>
+        <v>0.0007506835390813649</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0002111710928147659</v>
+        <v>0.01197544857859612</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0001042448639054783</v>
+        <v>0.003356171771883965</v>
       </c>
       <c r="FA16" t="n">
-        <v>5.717070598620921e-05</v>
+        <v>0.005877763032913208</v>
       </c>
       <c r="FB16" t="n">
-        <v>4.964388426742516e-05</v>
+        <v>0.000903288833796978</v>
       </c>
       <c r="FC16" t="n">
-        <v>4.557760621537454e-05</v>
+        <v>0.005699330009520054</v>
       </c>
       <c r="FD16" t="n">
-        <v>8.314280421473086e-05</v>
+        <v>0.0009121020557358861</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001354932901449502</v>
+        <v>0.000794422288890928</v>
       </c>
       <c r="FF16" t="n">
-        <v>7.210381590994075e-05</v>
+        <v>0.004285064060240984</v>
       </c>
       <c r="FG16" t="n">
-        <v>6.569868128281087e-05</v>
+        <v>0.004284283146262169</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.130351756728487e-05</v>
+        <v>0.0002538659609854221</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.000204478099476546</v>
+        <v>0.00685869250446558</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0001143027839134447</v>
+        <v>0.00294514512643218</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0001065230462700129</v>
+        <v>5.642138421535492e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0001495410542702302</v>
+        <v>0.01103018037974834</v>
       </c>
       <c r="FM16" t="n">
-        <v>6.078604201320559e-06</v>
+        <v>0.003921811934560537</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0001022393407765776</v>
+        <v>0.00890703871846199</v>
       </c>
       <c r="FO16" t="n">
-        <v>7.502325752284378e-05</v>
+        <v>0.02132498286664486</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0001868995896074921</v>
+        <v>0.0003418305423110723</v>
       </c>
       <c r="FQ16" t="n">
-        <v>2.495248190825805e-05</v>
+        <v>0.003219974227249622</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0002367871784372255</v>
+        <v>0.00110035203397274</v>
       </c>
       <c r="FS16" t="n">
-        <v>3.807336543104611e-05</v>
+        <v>0.003244993276894093</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0001447061513317749</v>
+        <v>0.008134212344884872</v>
       </c>
       <c r="FU16" t="n">
-        <v>6.609542469959706e-05</v>
+        <v>0.003486283589154482</v>
       </c>
       <c r="FV16" t="n">
-        <v>3.823870792984962e-05</v>
+        <v>0.00459055881947279</v>
       </c>
       <c r="FW16" t="n">
-        <v>1.530443114461377e-06</v>
+        <v>0.02384127303957939</v>
       </c>
       <c r="FX16" t="n">
-        <v>1.691376564849634e-05</v>
+        <v>0.002700160490348935</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0002291093696840107</v>
+        <v>0.001432353863492608</v>
       </c>
       <c r="FZ16" t="n">
-        <v>9.376340312883258e-05</v>
+        <v>0.0009813362266868353</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001315207919105887</v>
+        <v>0.01584786176681519</v>
       </c>
       <c r="GB16" t="n">
-        <v>4.661342245526612e-05</v>
+        <v>0.00122493936214596</v>
       </c>
       <c r="GC16" t="n">
-        <v>4.06546205340419e-05</v>
+        <v>0.01546382717788219</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0001466636313125491</v>
+        <v>0.007297397591173649</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0002653019037097692</v>
+        <v>0.005408594384789467</v>
       </c>
       <c r="GF16" t="n">
-        <v>3.391452992218547e-05</v>
+        <v>0.002502246294170618</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.000152897642692551</v>
+        <v>0.001661688787862659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0001249665656359866</v>
+        <v>8.527305972449994e-09</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003868176136165857</v>
+        <v>1.218767042843183e-08</v>
       </c>
       <c r="C17" t="n">
-        <v>9.836276876740158e-05</v>
+        <v>4.470361858466276e-10</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006247262936085463</v>
+        <v>3.893769306984041e-09</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001497651799581945</v>
+        <v>3.373014312302303e-09</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0004911727737635374</v>
+        <v>7.250302580530388e-09</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001788444060366601</v>
+        <v>8.725774547357901e-10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0005417066859081388</v>
+        <v>6.757512771571328e-09</v>
       </c>
       <c r="I17" t="n">
-        <v>2.488811878720298e-05</v>
+        <v>5.921224399685343e-09</v>
       </c>
       <c r="J17" t="n">
-        <v>3.765890141949058e-05</v>
+        <v>1.022926010563197e-08</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003379252506420016</v>
+        <v>1.366785795653414e-08</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0006403201259672642</v>
+        <v>5.017251059058481e-10</v>
       </c>
       <c r="M17" t="n">
-        <v>3.880217991536483e-05</v>
+        <v>4.066126990664998e-09</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0009862065780907869</v>
+        <v>3.56796858724806e-09</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0006737833609804511</v>
+        <v>6.055218548794983e-09</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0001403860806021839</v>
+        <v>2.029962448135691e-10</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001442421053070575</v>
+        <v>7.392531919947487e-09</v>
       </c>
       <c r="R17" t="n">
-        <v>3.168168041156605e-05</v>
+        <v>4.905283401690497e-10</v>
       </c>
       <c r="S17" t="n">
-        <v>3.705840208567679e-05</v>
+        <v>2.287760425545571e-09</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0004803587798960507</v>
+        <v>1.51178636276228e-09</v>
       </c>
       <c r="U17" t="n">
-        <v>7.85202719271183e-05</v>
+        <v>9.306432846578616e-10</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0004044164670631289</v>
+        <v>3.13256642847648e-10</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0007015583105385303</v>
+        <v>1.083836465021193e-09</v>
       </c>
       <c r="X17" t="n">
-        <v>0.000141356562380679</v>
+        <v>1.545450989404173e-09</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.002524166135117e-05</v>
+        <v>8.698752829161549e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0006655477918684483</v>
+        <v>4.277482368308938e-09</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0001770443341229111</v>
+        <v>2.842293955751529e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0002044109569396824</v>
+        <v>1.035204366672815e-09</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.011200745590031e-06</v>
+        <v>1.918087910723898e-09</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0001038252958096564</v>
+        <v>2.951226152347886e-09</v>
       </c>
       <c r="AE17" t="n">
-        <v>5.316311217029579e-05</v>
+        <v>1.934027160643836e-09</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0002557969419285655</v>
+        <v>8.642021542826228e-10</v>
       </c>
       <c r="AG17" t="n">
-        <v>6.943587504792958e-05</v>
+        <v>1.900652080166765e-09</v>
       </c>
       <c r="AH17" t="n">
-        <v>5.297542520565912e-05</v>
+        <v>1.091496115712687e-09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0001972133904928342</v>
+        <v>1.387904569050136e-09</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.000339683931088075</v>
+        <v>3.522835134717184e-09</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0006539238383993506</v>
+        <v>4.442531231774183e-09</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0004238486289978027</v>
+        <v>1.190225251690435e-09</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0001188211317639798</v>
+        <v>4.358383876024163e-09</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.100615165545605e-05</v>
+        <v>1.640637070643436e-09</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0004385246429592371</v>
+        <v>1.65822647280045e-10</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.000375264004105702</v>
+        <v>6.08311290228869e-10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.067332727368921e-06</v>
+        <v>6.246446693225494e-10</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0001436168095096946</v>
+        <v>4.439867362648897e-10</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.912053504493088e-05</v>
+        <v>1.297188051418985e-10</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.355700391693972e-05</v>
+        <v>8.635766768350095e-09</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.002568322466686368</v>
+        <v>4.027113087445855e-10</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0003314708592370152</v>
+        <v>4.023245736561876e-09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0002425499260425568</v>
+        <v>2.210751581799286e-09</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0008904673741199076</v>
+        <v>8.144526830733412e-09</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0003942878101952374</v>
+        <v>8.980642340894462e-10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0002780619543045759</v>
+        <v>1.138777294684701e-09</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0001000538759399205</v>
+        <v>3.306121487689495e-10</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.740870645036921e-05</v>
+        <v>6.547458131223038e-10</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0004744438629131764</v>
+        <v>2.469703108687327e-09</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.000923574436455965</v>
+        <v>7.10667702463752e-09</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0005980835994705558</v>
+        <v>9.754663743422043e-11</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0001395020808558911</v>
+        <v>2.399838994193715e-09</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0006391920032911003</v>
+        <v>8.632839332278763e-09</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0003957330191042274</v>
+        <v>5.178000694883167e-09</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0003678200591821223</v>
+        <v>7.072656349471629e-10</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0002154509274987504</v>
+        <v>2.211251182160368e-09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0001134665144491009</v>
+        <v>5.071209230322893e-09</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0003355027001816779</v>
+        <v>3.869925491173376e-10</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0007074463064782321</v>
+        <v>8.552655250682051e-10</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0003579319745767862</v>
+        <v>2.843611734970608e-10</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0001654216030146927</v>
+        <v>8.88635887097422e-10</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0004059695638716221</v>
+        <v>6.967128540757983e-10</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0002020283136516809</v>
+        <v>1.664834659020897e-10</v>
       </c>
       <c r="BR17" t="n">
-        <v>4.065080429427326e-05</v>
+        <v>1.621337397672562e-09</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0001159036037279293</v>
+        <v>1.237436930701108e-09</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0001726977934595197</v>
+        <v>1.686278894297288e-09</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.891526234336197e-05</v>
+        <v>5.883903142489544e-09</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001568268868140876</v>
+        <v>2.103654750396089e-10</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0002494979707989842</v>
+        <v>1.541981209385312e-09</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.0001440394553355873</v>
+        <v>2.404387522414453e-10</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0004767325590364635</v>
+        <v>6.096863014448672e-10</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0001882490905700251</v>
+        <v>8.163936193739119e-10</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0001822855265345424</v>
+        <v>1.258784187996298e-09</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.000142455828608945</v>
+        <v>2.130914333875467e-09</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0001074076644727029</v>
+        <v>1.199488730563303e-09</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0001107070711441338</v>
+        <v>1.471523458640434e-09</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.000606117770075798</v>
+        <v>2.97524760384249e-09</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0001425347290933132</v>
+        <v>4.269915809818059e-10</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0001071679871529341</v>
+        <v>1.487847733905312e-09</v>
       </c>
       <c r="CH17" t="n">
-        <v>3.936531720682979e-05</v>
+        <v>1.629515189449648e-09</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.257724306924501e-05</v>
+        <v>2.654119590772552e-09</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0001754867262206972</v>
+        <v>3.686464744578899e-10</v>
       </c>
       <c r="CK17" t="n">
-        <v>9.86686791293323e-05</v>
+        <v>1.039489050391751e-09</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.778869409463368e-05</v>
+        <v>1.083545808633346e-09</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0008421585662290454</v>
+        <v>1.598829069138219e-09</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0005413807230070233</v>
+        <v>7.108089672414053e-10</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0002414977498119697</v>
+        <v>2.992480041541512e-09</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0001831045374274254</v>
+        <v>1.353840706208587e-09</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0004864432848989964</v>
+        <v>2.704519275198436e-09</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0003917122085113078</v>
+        <v>2.10938644329417e-09</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0006204526289366186</v>
+        <v>9.887630714189299e-10</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0004868296382483095</v>
+        <v>1.596425103222998e-09</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0001204040090669878</v>
+        <v>2.136700594235208e-09</v>
       </c>
       <c r="CV17" t="n">
-        <v>9.1767986305058e-05</v>
+        <v>1.009202388324582e-09</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0004913857555948198</v>
+        <v>2.815180089044134e-09</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0002396461204625666</v>
+        <v>3.901781120418946e-10</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0002956481475848705</v>
+        <v>1.582355690921133e-09</v>
       </c>
       <c r="CZ17" t="n">
-        <v>7.333753455895931e-05</v>
+        <v>1.1331506843959e-09</v>
       </c>
       <c r="DA17" t="n">
-        <v>3.680675581563264e-05</v>
+        <v>2.451677971748722e-09</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0001426751259714365</v>
+        <v>3.510977064635767e-10</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0001769336085999385</v>
+        <v>1.95389082691122e-09</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.290769771207124e-05</v>
+        <v>1.233887325646776e-09</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0003477345744613558</v>
+        <v>1.054921927590158e-09</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0006204997189342976</v>
+        <v>5.21578469303563e-09</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.276839611819014e-05</v>
+        <v>4.80699258176287e-09</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001365111558698118</v>
+        <v>1.737832544534967e-09</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.000622734718490392</v>
+        <v>4.721417035113973e-09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0002375525946263224</v>
+        <v>1.567962981674498e-09</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.000241104542510584</v>
+        <v>3.127649694789625e-09</v>
       </c>
       <c r="DL17" t="n">
-        <v>9.795719961402938e-05</v>
+        <v>8.962319775207561e-11</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0001864591467892751</v>
+        <v>3.260355985190699e-09</v>
       </c>
       <c r="DN17" t="n">
-        <v>5.405749834608287e-05</v>
+        <v>2.564585210862447e-09</v>
       </c>
       <c r="DO17" t="n">
-        <v>6.303676491370425e-05</v>
+        <v>3.750465271679104e-09</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.000366669031791389</v>
+        <v>1.681469408154612e-09</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0002672391710802913</v>
+        <v>2.905604645775384e-09</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0002440823154756799</v>
+        <v>1.077398170679089e-09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0002537761174608022</v>
+        <v>1.078968359102817e-09</v>
       </c>
       <c r="DT17" t="n">
-        <v>4.942637679050677e-05</v>
+        <v>2.196136161813911e-09</v>
       </c>
       <c r="DU17" t="n">
-        <v>3.059209848288447e-05</v>
+        <v>2.084779682220983e-09</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.024833495146595e-05</v>
+        <v>1.683725603385255e-09</v>
       </c>
       <c r="DW17" t="n">
-        <v>3.93405971408356e-05</v>
+        <v>2.390005970909215e-09</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0004156583163421601</v>
+        <v>9.847577198129898e-10</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0002078880788758397</v>
+        <v>1.988020859045037e-09</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.727030267938972e-06</v>
+        <v>3.792289815507388e-10</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0003609322884585708</v>
+        <v>6.907267646738546e-09</v>
       </c>
       <c r="EB17" t="n">
-        <v>4.631440242519602e-05</v>
+        <v>1.703888918846985e-09</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.0001002766075544059</v>
+        <v>2.056040893094746e-09</v>
       </c>
       <c r="ED17" t="n">
-        <v>3.576544258976355e-05</v>
+        <v>1.998369913991382e-09</v>
       </c>
       <c r="EE17" t="n">
-        <v>2.640197271830402e-05</v>
+        <v>1.621787926175955e-09</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0003832211659755558</v>
+        <v>1.868452947917376e-09</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0006472521345131099</v>
+        <v>8.490261826921142e-10</v>
       </c>
       <c r="EH17" t="n">
-        <v>3.540120451361872e-05</v>
+        <v>1.830643636679952e-09</v>
       </c>
       <c r="EI17" t="n">
-        <v>1.282730227103457e-05</v>
+        <v>1.303735452928834e-10</v>
       </c>
       <c r="EJ17" t="n">
-        <v>4.619421088136733e-05</v>
+        <v>2.762244599718855e-11</v>
       </c>
       <c r="EK17" t="n">
-        <v>2.159756695618853e-05</v>
+        <v>1.999149068510064e-09</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0001016468595480546</v>
+        <v>5.6489907196422e-10</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0001358881127089262</v>
+        <v>8.586783506459028e-10</v>
       </c>
       <c r="EN17" t="n">
-        <v>3.283403202658519e-05</v>
+        <v>9.411632584388485e-10</v>
       </c>
       <c r="EO17" t="n">
-        <v>9.330290777143091e-05</v>
+        <v>4.363666095130725e-10</v>
       </c>
       <c r="EP17" t="n">
-        <v>5.421113746706396e-05</v>
+        <v>2.360510675813998e-09</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0004607366281561553</v>
+        <v>4.554902011122408e-10</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0003623258089646697</v>
+        <v>4.297081857007612e-10</v>
       </c>
       <c r="ES17" t="n">
-        <v>2.883210800064262e-05</v>
+        <v>2.629421569366741e-09</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.000149862389662303</v>
+        <v>2.55302468055163e-09</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0002211350365541875</v>
+        <v>1.358586576571952e-10</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0004465146630536765</v>
+        <v>1.573734698112617e-09</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0003069215454161167</v>
+        <v>3.777840262841892e-09</v>
       </c>
       <c r="EX17" t="n">
-        <v>6.902911991346627e-05</v>
+        <v>1.53182933004814e-09</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.0005298923351801932</v>
+        <v>3.589375463519673e-09</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0001857876632129773</v>
+        <v>9.495597363962105e-11</v>
       </c>
       <c r="FA17" t="n">
-        <v>5.650417369906791e-05</v>
+        <v>1.886355294189457e-09</v>
       </c>
       <c r="FB17" t="n">
-        <v>1.515471922175493e-06</v>
+        <v>1.792189618932127e-09</v>
       </c>
       <c r="FC17" t="n">
-        <v>8.809546125121415e-05</v>
+        <v>2.233726759115484e-09</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0002072813222184777</v>
+        <v>1.620055756212935e-10</v>
       </c>
       <c r="FE17" t="n">
-        <v>8.43853922560811e-05</v>
+        <v>2.095555950987205e-09</v>
       </c>
       <c r="FF17" t="n">
-        <v>4.25798752985429e-05</v>
+        <v>5.860369967081169e-10</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0001139033847721294</v>
+        <v>6.228823568044106e-10</v>
       </c>
       <c r="FH17" t="n">
-        <v>2.313108052476309e-05</v>
+        <v>2.718750558017291e-09</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0003852691152133048</v>
+        <v>3.458699993075243e-09</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.000282667635474354</v>
+        <v>1.18027521089914e-09</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0003843445447273552</v>
+        <v>3.983597451906462e-09</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0001782843755790964</v>
+        <v>2.387896325117822e-09</v>
       </c>
       <c r="FM17" t="n">
-        <v>9.614053124096245e-05</v>
+        <v>1.184947140409065e-10</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0001063381205312908</v>
+        <v>3.316011465415158e-09</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0002776558394543827</v>
+        <v>6.428504395472601e-10</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0003997875028289855</v>
+        <v>3.961002192909291e-09</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0005327918916009367</v>
+        <v>4.925776675435145e-09</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0004517521883826703</v>
+        <v>8.516439997663383e-09</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0001747551141306758</v>
+        <v>2.819688926791741e-09</v>
       </c>
       <c r="FT17" t="n">
-        <v>8.574272214900702e-06</v>
+        <v>2.20360307778833e-09</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0001349357335129753</v>
+        <v>1.446125552639899e-09</v>
       </c>
       <c r="FV17" t="n">
-        <v>9.410592610947788e-06</v>
+        <v>4.024406141667214e-09</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001590175379533321</v>
+        <v>1.905616109354469e-09</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0001024590310407802</v>
+        <v>2.826948675149765e-09</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0005127167096361518</v>
+        <v>2.010105193406275e-09</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0001963107060873881</v>
+        <v>3.558519257040871e-09</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0001022866053972393</v>
+        <v>3.77091380343586e-09</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0001255335082532838</v>
+        <v>6.384114348279013e-10</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0002646413340698928</v>
+        <v>5.832595739718727e-09</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0006028456846252084</v>
+        <v>1.552571182728002e-09</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.000551949255168438</v>
+        <v>1.552900474877106e-09</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0002710141707211733</v>
+        <v>1.274005456686211e-09</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0002056869125226513</v>
+        <v>2.384840103175634e-09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.408277502283454e-05</v>
+        <v>5.475449142977595e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001144577981904149</v>
+        <v>0.007209243252873421</v>
       </c>
       <c r="C18" t="n">
-        <v>9.008905180962756e-05</v>
+        <v>0.0004114933544769883</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0006947661750018597</v>
+        <v>0.00597032718360424</v>
       </c>
       <c r="E18" t="n">
-        <v>5.069307735539041e-05</v>
+        <v>0.00146239111199975</v>
       </c>
       <c r="F18" t="n">
-        <v>4.394125426188111e-06</v>
+        <v>0.008973400108516216</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001045923636411317</v>
+        <v>0.002945741172879934</v>
       </c>
       <c r="H18" t="n">
-        <v>6.168438994791359e-05</v>
+        <v>0.003712129546329379</v>
       </c>
       <c r="I18" t="n">
-        <v>9.638263145461679e-05</v>
+        <v>0.002952216425910592</v>
       </c>
       <c r="J18" t="n">
-        <v>6.067461072234437e-05</v>
+        <v>0.0004596076032612473</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0009694110485725105</v>
+        <v>0.008345644921064377</v>
       </c>
       <c r="L18" t="n">
-        <v>8.279030225821771e-06</v>
+        <v>0.001920708455145359</v>
       </c>
       <c r="M18" t="n">
-        <v>0.000673311878927052</v>
+        <v>0.007582433521747589</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0001623217685846612</v>
+        <v>0.002662214683368802</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0001244851591764018</v>
+        <v>0.009736546315252781</v>
       </c>
       <c r="P18" t="n">
-        <v>6.872281664982438e-05</v>
+        <v>0.001449732226319611</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001188285095850006</v>
+        <v>0.003032924374565482</v>
       </c>
       <c r="R18" t="n">
-        <v>3.286716673756018e-05</v>
+        <v>0.001430449308827519</v>
       </c>
       <c r="S18" t="n">
-        <v>9.661237709224224e-05</v>
+        <v>0.0001840378681663424</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0001157778679043986</v>
+        <v>0.0002259340835735202</v>
       </c>
       <c r="U18" t="n">
-        <v>4.814170461031608e-05</v>
+        <v>0.0008476085495203733</v>
       </c>
       <c r="V18" t="n">
-        <v>6.986539665376768e-05</v>
+        <v>0.0006773952627554536</v>
       </c>
       <c r="W18" t="n">
-        <v>5.002252510166727e-05</v>
+        <v>0.0004590578028000891</v>
       </c>
       <c r="X18" t="n">
-        <v>6.906525959493592e-05</v>
+        <v>0.001579598872922361</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.224587120115757e-05</v>
+        <v>0.001133210957050323</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0001025473902700469</v>
+        <v>0.001453119795769453</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.509566785302013e-05</v>
+        <v>0.0004019976768177003</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0001440609194105491</v>
+        <v>0.000633592251688242</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0002688619133550674</v>
+        <v>0.0007083053351379931</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.776504152279813e-05</v>
+        <v>0.001352379214949906</v>
       </c>
       <c r="AE18" t="n">
-        <v>5.474582212627865e-05</v>
+        <v>0.0009975482244044542</v>
       </c>
       <c r="AF18" t="n">
-        <v>7.280113641172647e-05</v>
+        <v>0.0001455873134545982</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.778182195266709e-06</v>
+        <v>0.00310291675850749</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.581076740985736e-05</v>
+        <v>0.0002023826236836612</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.272869889769936e-06</v>
+        <v>0.003621244570240378</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.876088936114684e-05</v>
+        <v>0.000107829189801123</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.004842488327995e-06</v>
+        <v>0.0005219306331127882</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0001026326499413699</v>
+        <v>0.001017460133880377</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.369584737811238e-05</v>
+        <v>0.001233381452038884</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.904312375700101e-05</v>
+        <v>0.001204732805490494</v>
       </c>
       <c r="AO18" t="n">
-        <v>9.567470988258719e-05</v>
+        <v>0.0001519261277280748</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.688267214689404e-05</v>
+        <v>0.0003320709511172026</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.107147343456745e-05</v>
+        <v>0.0001120546949096024</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.750701216631569e-05</v>
+        <v>0.0005789260612800717</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.97563276742585e-05</v>
+        <v>0.0007751616649329662</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0001280878495890647</v>
+        <v>0.001206497428938746</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0007529962458647788</v>
+        <v>0.00335434777662158</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.000147232145536691</v>
+        <v>0.001643773051910102</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.0002528811746742576</v>
+        <v>0.002658159472048283</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.092340067378245e-06</v>
+        <v>0.006672651972621679</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.307084110332653e-05</v>
+        <v>0.00515531562268734</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.540968464221805e-06</v>
+        <v>0.0001600277610123158</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.049924660241231e-05</v>
+        <v>0.0009359533432871103</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.778729362442391e-06</v>
+        <v>0.0005625407793559134</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.900441414676607e-05</v>
+        <v>0.0002489418548066169</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0001844162325141951</v>
+        <v>0.002375805051997304</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.0002372921298956499</v>
+        <v>0.001409887801855803</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.0001060095382854342</v>
+        <v>0.00110958400182426</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.390039485879242e-05</v>
+        <v>0.004060546401888132</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.0001248042972292751</v>
+        <v>0.001664391485974193</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.0001006188394967467</v>
+        <v>0.0009267404675483704</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9.555040014674887e-05</v>
+        <v>0.003954239655286074</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.926192948711105e-05</v>
+        <v>0.001278188545256853</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.0001037265319610015</v>
+        <v>0.0002286445087520406</v>
       </c>
       <c r="BM18" t="n">
-        <v>7.688572077313438e-05</v>
+        <v>0.0002592967357486486</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.0001340703893220052</v>
+        <v>6.683371611870825e-05</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.504306939954404e-05</v>
+        <v>0.001899833790957928</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0001828768581617624</v>
+        <v>5.309397238306701e-06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.355937951710075e-05</v>
+        <v>0.001466049114242196</v>
       </c>
       <c r="BR18" t="n">
-        <v>7.222055864986032e-05</v>
+        <v>0.0002833491307683289</v>
       </c>
       <c r="BS18" t="n">
-        <v>3.513916453812271e-05</v>
+        <v>0.001849440857768059</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.354720244416967e-05</v>
+        <v>0.001147749368101358</v>
       </c>
       <c r="BU18" t="n">
-        <v>9.321197285316885e-05</v>
+        <v>0.0005301135824993253</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0003723172703757882</v>
+        <v>0.001767890062183142</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.58103487896733e-05</v>
+        <v>0.0008477560477331281</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0001467454567318782</v>
+        <v>0.002416204195469618</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.746939031174406e-05</v>
+        <v>0.001816174597479403</v>
       </c>
       <c r="BZ18" t="n">
-        <v>8.03125585662201e-05</v>
+        <v>0.002727333921939135</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.184370507369749e-05</v>
+        <v>0.001540685771033168</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.852493344107643e-05</v>
+        <v>8.338101906701922e-05</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.956523116561584e-05</v>
+        <v>0.000819340581074357</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.779551348590758e-05</v>
+        <v>0.0002332021831534803</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.0002104489394696429</v>
+        <v>0.002096600830554962</v>
       </c>
       <c r="CF18" t="n">
-        <v>4.779360097018071e-05</v>
+        <v>9.61163459578529e-05</v>
       </c>
       <c r="CG18" t="n">
-        <v>8.778316987445578e-05</v>
+        <v>0.002067075576633215</v>
       </c>
       <c r="CH18" t="n">
-        <v>5.037145820097066e-05</v>
+        <v>0.0002426754217594862</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.628284164529759e-06</v>
+        <v>0.002367845736443996</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.758344453468453e-05</v>
+        <v>2.237051376141608e-05</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.210764730785741e-05</v>
+        <v>0.0005129748024046421</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.865256490418687e-05</v>
+        <v>0.001095582963898778</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.0002451503823976964</v>
+        <v>0.0001716430415399373</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0001330024970229715</v>
+        <v>0.0005045714206062257</v>
       </c>
       <c r="CO18" t="n">
-        <v>2.543839218560606e-05</v>
+        <v>0.002867648145183921</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0001797659060684964</v>
+        <v>0.002074587158858776</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0001986244751606137</v>
+        <v>0.003257209900766611</v>
       </c>
       <c r="CR18" t="n">
-        <v>8.762424840824679e-05</v>
+        <v>0.0009218968916684389</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0001025521123665385</v>
+        <v>0.0005358793423511088</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0001970319863175973</v>
+        <v>0.0006762837874703109</v>
       </c>
       <c r="CU18" t="n">
-        <v>6.278410182858352e-06</v>
+        <v>0.0007428426761180162</v>
       </c>
       <c r="CV18" t="n">
-        <v>7.947517588036135e-06</v>
+        <v>0.0003439023275859654</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.0002094082883559167</v>
+        <v>0.001969421748071909</v>
       </c>
       <c r="CX18" t="n">
-        <v>8.124487794702873e-05</v>
+        <v>0.0002467101148795336</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.0001181604893645272</v>
+        <v>0.002285072114318609</v>
       </c>
       <c r="CZ18" t="n">
-        <v>5.459087697090581e-05</v>
+        <v>0.0005040469695813954</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.426704122626688e-05</v>
+        <v>0.002502718241885304</v>
       </c>
       <c r="DB18" t="n">
-        <v>3.048015605600085e-05</v>
+        <v>0.0002044757129624486</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.07816392503446e-05</v>
+        <v>0.000410553504480049</v>
       </c>
       <c r="DD18" t="n">
-        <v>5.655311724694911e-06</v>
+        <v>0.0007739789434708655</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.0001391454425174743</v>
+        <v>0.0004011738346889615</v>
       </c>
       <c r="DF18" t="n">
-        <v>4.260542482370511e-05</v>
+        <v>0.001808445900678635</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.133553011342883e-05</v>
+        <v>0.002614437602460384</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.000213533901842311</v>
+        <v>0.0009232634329237044</v>
       </c>
       <c r="DI18" t="n">
-        <v>5.458637315314263e-05</v>
+        <v>0.001593678258359432</v>
       </c>
       <c r="DJ18" t="n">
-        <v>9.841154678724706e-06</v>
+        <v>0.00248977611772716</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.336417648824863e-06</v>
+        <v>0.0002860409731511027</v>
       </c>
       <c r="DL18" t="n">
-        <v>7.405684300465509e-05</v>
+        <v>0.001663260278292</v>
       </c>
       <c r="DM18" t="n">
-        <v>5.503986903931946e-05</v>
+        <v>0.001266476465389132</v>
       </c>
       <c r="DN18" t="n">
-        <v>3.288207881269045e-05</v>
+        <v>0.0008136248216032982</v>
       </c>
       <c r="DO18" t="n">
-        <v>5.450794560601935e-05</v>
+        <v>0.002140191849321127</v>
       </c>
       <c r="DP18" t="n">
-        <v>8.370215073227882e-05</v>
+        <v>0.00128638930618763</v>
       </c>
       <c r="DQ18" t="n">
-        <v>4.914311648462899e-05</v>
+        <v>0.001307280035689473</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0001187483430840075</v>
+        <v>0.0002146101032849401</v>
       </c>
       <c r="DS18" t="n">
-        <v>1.548311593069229e-05</v>
+        <v>0.0009489060612395406</v>
       </c>
       <c r="DT18" t="n">
-        <v>3.700768138514832e-05</v>
+        <v>0.001088219694793224</v>
       </c>
       <c r="DU18" t="n">
-        <v>3.931271567125805e-05</v>
+        <v>0.00187591603025794</v>
       </c>
       <c r="DV18" t="n">
-        <v>5.714667349820957e-05</v>
+        <v>0.001636137720197439</v>
       </c>
       <c r="DW18" t="n">
-        <v>5.510651317308657e-05</v>
+        <v>0.0006125220097601414</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0001728328206809238</v>
+        <v>0.000900211394764483</v>
       </c>
       <c r="DY18" t="n">
-        <v>4.485156750888564e-06</v>
+        <v>0.001481007668189704</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.930225547170267e-05</v>
+        <v>0.0005635982379317284</v>
       </c>
       <c r="EA18" t="n">
-        <v>8.215229900088161e-05</v>
+        <v>0.0007189686875790358</v>
       </c>
       <c r="EB18" t="n">
-        <v>4.11438086302951e-05</v>
+        <v>0.0006004640599712729</v>
       </c>
       <c r="EC18" t="n">
-        <v>5.013807458453812e-05</v>
+        <v>0.0004912091535516083</v>
       </c>
       <c r="ED18" t="n">
-        <v>3.238062345189974e-05</v>
+        <v>0.002290863776579499</v>
       </c>
       <c r="EE18" t="n">
-        <v>1.787780274753459e-05</v>
+        <v>0.001957651926204562</v>
       </c>
       <c r="EF18" t="n">
-        <v>1.017374597722664e-05</v>
+        <v>7.645630103070289e-05</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0001916957553476095</v>
+        <v>0.001619418384507298</v>
       </c>
       <c r="EH18" t="n">
-        <v>8.545852324459702e-05</v>
+        <v>0.001449144328944385</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.0001491655712015927</v>
+        <v>0.001117801177315414</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0001380762550979853</v>
+        <v>0.001073490595445037</v>
       </c>
       <c r="EK18" t="n">
-        <v>4.005398295703344e-06</v>
+        <v>0.002052785130217671</v>
       </c>
       <c r="EL18" t="n">
-        <v>2.095560557791032e-05</v>
+        <v>0.0004391200200188905</v>
       </c>
       <c r="EM18" t="n">
-        <v>3.199244747520424e-05</v>
+        <v>0.0008773732115514576</v>
       </c>
       <c r="EN18" t="n">
-        <v>1.641512972128112e-05</v>
+        <v>0.0005498949903994799</v>
       </c>
       <c r="EO18" t="n">
-        <v>7.316655683098361e-06</v>
+        <v>0.0007421124028041959</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0002431073226034641</v>
+        <v>0.001663394388742745</v>
       </c>
       <c r="EQ18" t="n">
-        <v>8.969190093921497e-05</v>
+        <v>0.0009446869371458888</v>
       </c>
       <c r="ER18" t="n">
-        <v>5.141478322912008e-05</v>
+        <v>0.002209713216871023</v>
       </c>
       <c r="ES18" t="n">
-        <v>3.195879253325984e-05</v>
+        <v>0.001066897995769978</v>
       </c>
       <c r="ET18" t="n">
-        <v>1.931770020746626e-05</v>
+        <v>0.0001642657734919339</v>
       </c>
       <c r="EU18" t="n">
-        <v>6.526082142954692e-05</v>
+        <v>0.0004400578327476978</v>
       </c>
       <c r="EV18" t="n">
-        <v>1.792196417227387e-05</v>
+        <v>0.0006878377171233296</v>
       </c>
       <c r="EW18" t="n">
-        <v>4.453399014892057e-05</v>
+        <v>0.00162464112509042</v>
       </c>
       <c r="EX18" t="n">
-        <v>3.679354631458409e-05</v>
+        <v>0.0003025837359018624</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0002170478401239961</v>
+        <v>0.002520188223570585</v>
       </c>
       <c r="EZ18" t="n">
-        <v>4.544567127595656e-05</v>
+        <v>3.604738594731316e-05</v>
       </c>
       <c r="FA18" t="n">
-        <v>9.703264367999509e-05</v>
+        <v>0.002418260555714369</v>
       </c>
       <c r="FB18" t="n">
-        <v>3.322424890939146e-05</v>
+        <v>0.0001109361037379131</v>
       </c>
       <c r="FC18" t="n">
-        <v>2.489359576429706e-05</v>
+        <v>0.002173896413296461</v>
       </c>
       <c r="FD18" t="n">
-        <v>2.113794835167937e-05</v>
+        <v>1.076870830729604e-06</v>
       </c>
       <c r="FE18" t="n">
-        <v>1.768958100001328e-06</v>
+        <v>0.0004513089661486447</v>
       </c>
       <c r="FF18" t="n">
-        <v>1.292607157665771e-05</v>
+        <v>0.0004487551341298968</v>
       </c>
       <c r="FG18" t="n">
-        <v>3.751036638277583e-05</v>
+        <v>0.0001382965128868818</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.000140382515382953</v>
+        <v>0.001197111210785806</v>
       </c>
       <c r="FI18" t="n">
-        <v>7.408091187244281e-05</v>
+        <v>0.002588902832940221</v>
       </c>
       <c r="FJ18" t="n">
-        <v>5.688206510967575e-05</v>
+        <v>0.002074936404824257</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.0001003846264211461</v>
+        <v>0.0005882225232198834</v>
       </c>
       <c r="FL18" t="n">
-        <v>4.422290294314735e-05</v>
+        <v>0.002624577842652798</v>
       </c>
       <c r="FM18" t="n">
-        <v>6.233585008885711e-05</v>
+        <v>0.0001111890451284125</v>
       </c>
       <c r="FN18" t="n">
-        <v>5.101818169350736e-05</v>
+        <v>0.001809860463254154</v>
       </c>
       <c r="FO18" t="n">
-        <v>1.310609877691604e-05</v>
+        <v>0.002066230634227395</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.0001237559772562236</v>
+        <v>0.0009102160693146288</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.0001290381042053923</v>
+        <v>0.0003839939599856734</v>
       </c>
       <c r="FR18" t="n">
-        <v>9.953112021321431e-05</v>
+        <v>0.004291885066777468</v>
       </c>
       <c r="FS18" t="n">
-        <v>6.117014709161595e-05</v>
+        <v>0.0001065130127244629</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.0001062958617694676</v>
+        <v>0.0009037568233907223</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0001173694327007979</v>
+        <v>0.001121725421398878</v>
       </c>
       <c r="FV18" t="n">
-        <v>3.559636388672516e-05</v>
+        <v>0.00056970224250108</v>
       </c>
       <c r="FW18" t="n">
-        <v>6.148120883153751e-05</v>
+        <v>0.001715675345622003</v>
       </c>
       <c r="FX18" t="n">
-        <v>3.437186751398258e-05</v>
+        <v>0.001949927071109414</v>
       </c>
       <c r="FY18" t="n">
-        <v>8.293368591694161e-05</v>
+        <v>0.0006910819793120027</v>
       </c>
       <c r="FZ18" t="n">
-        <v>5.901184340473264e-05</v>
+        <v>0.001687851967290044</v>
       </c>
       <c r="GA18" t="n">
-        <v>3.358396497787908e-05</v>
+        <v>0.002377742901444435</v>
       </c>
       <c r="GB18" t="n">
-        <v>5.542150029214099e-05</v>
+        <v>0.0006850589998066425</v>
       </c>
       <c r="GC18" t="n">
-        <v>3.633194137364626e-05</v>
+        <v>0.004138852935284376</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.0001386779767926782</v>
+        <v>0.00383151788264513</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.0001559835800435394</v>
+        <v>0.0007437053136527538</v>
       </c>
       <c r="GF18" t="n">
-        <v>5.881403922103345e-05</v>
+        <v>0.0002825551782734692</v>
       </c>
       <c r="GG18" t="n">
-        <v>9.901988232741132e-05</v>
+        <v>0.0004257845575921237</v>
       </c>
     </row>
     <row r="19">
@@ -11241,571 +11241,571 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.550500201119576e-05</v>
+        <v>0.05168557912111282</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0005127161275595427</v>
+        <v>0.6011913418769836</v>
       </c>
       <c r="C20" t="n">
-        <v>6.337924787658267e-06</v>
+        <v>0.02656630240380764</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001516618358436972</v>
+        <v>0.1775253415107727</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0001039557319018058</v>
+        <v>0.1990625411272049</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002040562249021605</v>
+        <v>0.009934328496456146</v>
       </c>
       <c r="G20" t="n">
-        <v>5.863129990757443e-05</v>
+        <v>0.04839101806282997</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0001654067600611597</v>
+        <v>0.08680093288421631</v>
       </c>
       <c r="I20" t="n">
-        <v>7.21042015356943e-05</v>
+        <v>0.07341671735048294</v>
       </c>
       <c r="J20" t="n">
-        <v>8.453101327177137e-05</v>
+        <v>0.02415493130683899</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000461853458546102</v>
+        <v>0.7532019019126892</v>
       </c>
       <c r="L20" t="n">
-        <v>4.308296047383919e-05</v>
+        <v>0.06872817128896713</v>
       </c>
       <c r="M20" t="n">
-        <v>5.423289985628799e-05</v>
+        <v>0.2973628640174866</v>
       </c>
       <c r="N20" t="n">
-        <v>5.222506842983421e-06</v>
+        <v>0.004954829812049866</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0002077783283311874</v>
+        <v>0.01980531215667725</v>
       </c>
       <c r="P20" t="n">
-        <v>8.164947212208062e-05</v>
+        <v>0.0001979470252990723</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.28352858661674e-06</v>
+        <v>0.1379066854715347</v>
       </c>
       <c r="R20" t="n">
-        <v>9.726442658575252e-05</v>
+        <v>0.06884324550628662</v>
       </c>
       <c r="S20" t="n">
-        <v>1.385243649565382e-05</v>
+        <v>0.03502894565463066</v>
       </c>
       <c r="T20" t="n">
-        <v>4.34410831076093e-05</v>
+        <v>0.09738644957542419</v>
       </c>
       <c r="U20" t="n">
-        <v>3.263719554524869e-05</v>
+        <v>0.05015347525477409</v>
       </c>
       <c r="V20" t="n">
-        <v>5.444062844617292e-05</v>
+        <v>0.08904401957988739</v>
       </c>
       <c r="W20" t="n">
-        <v>7.546448614448309e-05</v>
+        <v>0.07238367944955826</v>
       </c>
       <c r="X20" t="n">
-        <v>4.873979196418077e-05</v>
+        <v>0.01762713119387627</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.223785461159423e-05</v>
+        <v>0.0786491259932518</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.479009218513966e-05</v>
+        <v>0.1703144162893295</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.217615398578346e-05</v>
+        <v>0.02993478253483772</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85219178092666e-05</v>
+        <v>0.00294961966574192</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.864547968783882e-05</v>
+        <v>0.0195755623281002</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.46150331501849e-05</v>
+        <v>0.1255358159542084</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.137517301685875e-05</v>
+        <v>0.2178937196731567</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.098430897807702e-05</v>
+        <v>0.1654509305953979</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.695594386954326e-06</v>
+        <v>0.02598021924495697</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.238929326063953e-05</v>
+        <v>0.02498956955969334</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.594977483269759e-05</v>
+        <v>0.1668076813220978</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.823877705144696e-06</v>
+        <v>0.06619276106357574</v>
       </c>
       <c r="AK20" t="n">
-        <v>6.711645983159542e-05</v>
+        <v>0.1000049859285355</v>
       </c>
       <c r="AL20" t="n">
-        <v>7.233830547193065e-05</v>
+        <v>0.09627345949411392</v>
       </c>
       <c r="AM20" t="n">
-        <v>8.763240657572169e-07</v>
+        <v>0.08127546310424805</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.026990088983439e-05</v>
+        <v>0.06841091066598892</v>
       </c>
       <c r="AO20" t="n">
-        <v>8.790449101070408e-06</v>
+        <v>0.01305397227406502</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.780272426316515e-05</v>
+        <v>0.004937093704938889</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.534564893925563e-05</v>
+        <v>0.09206630289554596</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.308145824121311e-05</v>
+        <v>0.1968380212783813</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.850791421835311e-05</v>
+        <v>0.03878490999341011</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.11060068977531e-06</v>
+        <v>0.1813680529594421</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.0003038653521798551</v>
+        <v>0.5042177438735962</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.091091952635907e-05</v>
+        <v>0.07868832349777222</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.984075712854974e-05</v>
+        <v>0.2220492362976074</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.034021498635411e-05</v>
+        <v>0.2516067028045654</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.0001337895228061825</v>
+        <v>0.0773124098777771</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.0001140639142249711</v>
+        <v>0.02784054167568684</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.366867016069591e-05</v>
+        <v>0.06191462278366089</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.217942715622485e-05</v>
+        <v>0.07321999967098236</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.515677912626415e-06</v>
+        <v>0.1418801993131638</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.0001148059964179993</v>
+        <v>0.0328940711915493</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.000111396650027018</v>
+        <v>0.05965974554419518</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.098389035789296e-05</v>
+        <v>0.02031303942203522</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.821465750457719e-05</v>
+        <v>0.06623611599206924</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.131209763931111e-05</v>
+        <v>0.03050932660698891</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.04457314289175e-05</v>
+        <v>0.18305703997612</v>
       </c>
       <c r="BJ20" t="n">
-        <v>7.937414920888841e-05</v>
+        <v>0.1694552898406982</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.564881186932325e-05</v>
+        <v>0.08052337914705276</v>
       </c>
       <c r="BL20" t="n">
-        <v>2.923755710071418e-05</v>
+        <v>0.06252489984035492</v>
       </c>
       <c r="BM20" t="n">
-        <v>5.302226418280043e-05</v>
+        <v>0.04824116080999374</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.144297392689623e-05</v>
+        <v>0.04894037544727325</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.097095057251863e-05</v>
+        <v>0.0699533224105835</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.34138097363757e-06</v>
+        <v>0.1600662022829056</v>
       </c>
       <c r="BQ20" t="n">
-        <v>2.747930557234213e-05</v>
+        <v>0.0002505570009816438</v>
       </c>
       <c r="BR20" t="n">
-        <v>6.072054384276271e-05</v>
+        <v>0.1828694939613342</v>
       </c>
       <c r="BS20" t="n">
-        <v>2.359173595323227e-05</v>
+        <v>0.07555840164422989</v>
       </c>
       <c r="BT20" t="n">
-        <v>1.286608494410757e-05</v>
+        <v>0.12154620885849</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.478342816582881e-06</v>
+        <v>0.08741423487663269</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.0001835147850215435</v>
+        <v>0.3046643137931824</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.831232167314738e-05</v>
+        <v>0.09792131185531616</v>
       </c>
       <c r="BX20" t="n">
-        <v>4.874527803622186e-06</v>
+        <v>0.1002838611602783</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.175885260337964e-05</v>
+        <v>0.02649367228150368</v>
       </c>
       <c r="BZ20" t="n">
-        <v>5.938156027696095e-05</v>
+        <v>0.002091461792588234</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.064586391905323e-07</v>
+        <v>0.1288148015737534</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.380634941800963e-05</v>
+        <v>0.06010345369577408</v>
       </c>
       <c r="CC20" t="n">
-        <v>6.062912871129811e-05</v>
+        <v>0.03837532922625542</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.333895049057901e-06</v>
+        <v>0.0134234856814146</v>
       </c>
       <c r="CE20" t="n">
-        <v>9.143551869783551e-05</v>
+        <v>0.1918596476316452</v>
       </c>
       <c r="CF20" t="n">
-        <v>4.460943819140084e-05</v>
+        <v>0.01709822192788124</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.722478348005097e-05</v>
+        <v>0.0236321147531271</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.5124591300264e-05</v>
+        <v>0.01950725913047791</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.248045191459823e-05</v>
+        <v>0.01868217810988426</v>
       </c>
       <c r="CJ20" t="n">
-        <v>3.460405423538759e-05</v>
+        <v>0.02357287704944611</v>
       </c>
       <c r="CK20" t="n">
-        <v>2.234468774986453e-05</v>
+        <v>0.03947960957884789</v>
       </c>
       <c r="CL20" t="n">
-        <v>4.904501838609576e-05</v>
+        <v>0.007615658454596996</v>
       </c>
       <c r="CM20" t="n">
-        <v>6.316610233625397e-05</v>
+        <v>0.02533257938921452</v>
       </c>
       <c r="CN20" t="n">
-        <v>5.410677840700373e-05</v>
+        <v>0.1418206244707108</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.369095298286993e-05</v>
+        <v>0.06863545626401901</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.0001347056968370453</v>
+        <v>0.1206311583518982</v>
       </c>
       <c r="CQ20" t="n">
-        <v>6.840496644144878e-05</v>
+        <v>0.124967947602272</v>
       </c>
       <c r="CR20" t="n">
-        <v>6.915810809005052e-05</v>
+        <v>0.01928186044096947</v>
       </c>
       <c r="CS20" t="n">
-        <v>9.991737169912085e-05</v>
+        <v>0.1441674530506134</v>
       </c>
       <c r="CT20" t="n">
-        <v>6.914306140970439e-05</v>
+        <v>0.08244511485099792</v>
       </c>
       <c r="CU20" t="n">
-        <v>3.706922143464908e-05</v>
+        <v>0.04664375633001328</v>
       </c>
       <c r="CV20" t="n">
-        <v>4.805613116332097e-06</v>
+        <v>0.03250417858362198</v>
       </c>
       <c r="CW20" t="n">
-        <v>8.137537952279672e-05</v>
+        <v>0.1771021485328674</v>
       </c>
       <c r="CX20" t="n">
-        <v>4.979349614586681e-05</v>
+        <v>0.02907192148268223</v>
       </c>
       <c r="CY20" t="n">
-        <v>5.326647806214169e-05</v>
+        <v>0.06658336520195007</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.218765075667761e-05</v>
+        <v>0.05906595289707184</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.267427796847187e-05</v>
+        <v>0.03125095367431641</v>
       </c>
       <c r="DB20" t="n">
-        <v>3.727547300513834e-05</v>
+        <v>6.125494837760925e-05</v>
       </c>
       <c r="DC20" t="n">
-        <v>4.259499837644398e-05</v>
+        <v>0.03564213588833809</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.313770841690712e-05</v>
+        <v>0.02171437814831734</v>
       </c>
       <c r="DE20" t="n">
-        <v>4.709084532805718e-05</v>
+        <v>0.02150282263755798</v>
       </c>
       <c r="DF20" t="n">
-        <v>8.267715747933835e-05</v>
+        <v>0.04203056544065475</v>
       </c>
       <c r="DG20" t="n">
-        <v>5.540507117984816e-06</v>
+        <v>0.02972458675503731</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.0002361258084420115</v>
+        <v>0.09615409374237061</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.0001252373185707256</v>
+        <v>0.3227706849575043</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.0001785626373020932</v>
+        <v>0.06977637112140656</v>
       </c>
       <c r="DK20" t="n">
-        <v>7.847024244256318e-05</v>
+        <v>0.03392781317234039</v>
       </c>
       <c r="DL20" t="n">
-        <v>8.302400965476409e-05</v>
+        <v>0.113826647400856</v>
       </c>
       <c r="DM20" t="n">
-        <v>7.895268936408684e-05</v>
+        <v>0.1813711225986481</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.19997873500688e-05</v>
+        <v>0.0459730327129364</v>
       </c>
       <c r="DO20" t="n">
-        <v>3.492371615720913e-05</v>
+        <v>0.02441104501485825</v>
       </c>
       <c r="DP20" t="n">
-        <v>4.08498672186397e-05</v>
+        <v>0.02043340913951397</v>
       </c>
       <c r="DQ20" t="n">
-        <v>1.452378364774631e-05</v>
+        <v>0.05504104495048523</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.696282409597188e-06</v>
+        <v>0.119002491235733</v>
       </c>
       <c r="DS20" t="n">
-        <v>3.262631798861548e-05</v>
+        <v>0.06268221139907837</v>
       </c>
       <c r="DT20" t="n">
-        <v>4.44957877334673e-05</v>
+        <v>0.1785934269428253</v>
       </c>
       <c r="DU20" t="n">
-        <v>2.893889723054599e-05</v>
+        <v>0.02135967835783958</v>
       </c>
       <c r="DV20" t="n">
-        <v>2.481209412508179e-05</v>
+        <v>0.1387789696455002</v>
       </c>
       <c r="DW20" t="n">
-        <v>1.562979196023662e-05</v>
+        <v>0.07930327206850052</v>
       </c>
       <c r="DX20" t="n">
-        <v>2.909154864028096e-05</v>
+        <v>0.02729667723178864</v>
       </c>
       <c r="DY20" t="n">
-        <v>5.810468428535387e-05</v>
+        <v>0.005595753435045481</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.435821054154076e-05</v>
+        <v>0.06998182088136673</v>
       </c>
       <c r="EA20" t="n">
-        <v>5.356703695724718e-06</v>
+        <v>0.006653457880020142</v>
       </c>
       <c r="EB20" t="n">
-        <v>3.168445618939586e-05</v>
+        <v>0.04270472377538681</v>
       </c>
       <c r="EC20" t="n">
-        <v>6.247513738344423e-06</v>
+        <v>0.04377730563282967</v>
       </c>
       <c r="ED20" t="n">
-        <v>2.282685454702005e-05</v>
+        <v>0.1910985261201859</v>
       </c>
       <c r="EE20" t="n">
-        <v>7.910808926681057e-05</v>
+        <v>0.1488259434700012</v>
       </c>
       <c r="EF20" t="n">
-        <v>2.399622280790936e-05</v>
+        <v>0.05794965103268623</v>
       </c>
       <c r="EG20" t="n">
-        <v>9.34709096327424e-05</v>
+        <v>0.1182228401303291</v>
       </c>
       <c r="EH20" t="n">
-        <v>1.443707515136339e-05</v>
+        <v>0.05707023665308952</v>
       </c>
       <c r="EI20" t="n">
-        <v>1.873192377388477e-05</v>
+        <v>0.0268856305629015</v>
       </c>
       <c r="EJ20" t="n">
-        <v>6.345194560708478e-05</v>
+        <v>0.06065090000629425</v>
       </c>
       <c r="EK20" t="n">
-        <v>3.368274337844923e-05</v>
+        <v>0.03226448595523834</v>
       </c>
       <c r="EL20" t="n">
-        <v>4.337088466854766e-05</v>
+        <v>0.04213003814220428</v>
       </c>
       <c r="EM20" t="n">
-        <v>3.571959496184718e-06</v>
+        <v>0.07599250227212906</v>
       </c>
       <c r="EN20" t="n">
-        <v>2.315322490176186e-05</v>
+        <v>0.04835078120231628</v>
       </c>
       <c r="EO20" t="n">
-        <v>1.101165253203362e-06</v>
+        <v>0.07180389016866684</v>
       </c>
       <c r="EP20" t="n">
-        <v>5.238272569840774e-05</v>
+        <v>0.09043675661087036</v>
       </c>
       <c r="EQ20" t="n">
-        <v>9.8613221780397e-05</v>
+        <v>0.005965039134025574</v>
       </c>
       <c r="ER20" t="n">
-        <v>9.846196189755574e-05</v>
+        <v>0.01951106265187263</v>
       </c>
       <c r="ES20" t="n">
-        <v>6.801622657803819e-05</v>
+        <v>0.0918264165520668</v>
       </c>
       <c r="ET20" t="n">
-        <v>2.138650415872689e-05</v>
+        <v>0.0007307045161724091</v>
       </c>
       <c r="EU20" t="n">
-        <v>9.631617285776883e-05</v>
+        <v>0.01781386509537697</v>
       </c>
       <c r="EV20" t="n">
-        <v>0.0001037563342833892</v>
+        <v>0.05448741093277931</v>
       </c>
       <c r="EW20" t="n">
-        <v>7.995271516847424e-06</v>
+        <v>0.003652847371995449</v>
       </c>
       <c r="EX20" t="n">
-        <v>1.623555817786837e-06</v>
+        <v>0.0009272657334804535</v>
       </c>
       <c r="EY20" t="n">
-        <v>7.884585647843778e-05</v>
+        <v>0.2062731832265854</v>
       </c>
       <c r="EZ20" t="n">
-        <v>3.979816028731875e-05</v>
+        <v>0.02065153233706951</v>
       </c>
       <c r="FA20" t="n">
-        <v>1.582194636284839e-05</v>
+        <v>0.0482037253677845</v>
       </c>
       <c r="FB20" t="n">
-        <v>3.052682586712763e-05</v>
+        <v>0.08056836575269699</v>
       </c>
       <c r="FC20" t="n">
-        <v>1.422074547008378e-05</v>
+        <v>0.01647572964429855</v>
       </c>
       <c r="FD20" t="n">
-        <v>6.408242916222662e-05</v>
+        <v>0.02763139829039574</v>
       </c>
       <c r="FE20" t="n">
-        <v>4.306792834540829e-05</v>
+        <v>0.03475558012723923</v>
       </c>
       <c r="FF20" t="n">
-        <v>5.967739707557485e-05</v>
+        <v>0.03393106162548065</v>
       </c>
       <c r="FG20" t="n">
-        <v>2.351411603740416e-05</v>
+        <v>0.03011824935674667</v>
       </c>
       <c r="FH20" t="n">
-        <v>1.828174845286412e-06</v>
+        <v>0.2264510691165924</v>
       </c>
       <c r="FI20" t="n">
-        <v>8.790862193563953e-05</v>
+        <v>0.01859267055988312</v>
       </c>
       <c r="FJ20" t="n">
-        <v>4.875326339970343e-05</v>
+        <v>0.1553203463554382</v>
       </c>
       <c r="FK20" t="n">
-        <v>1.437653918401338e-05</v>
+        <v>0.05266086012125015</v>
       </c>
       <c r="FL20" t="n">
-        <v>1.69077429745812e-05</v>
+        <v>0.07480037957429886</v>
       </c>
       <c r="FM20" t="n">
-        <v>4.077191624674015e-05</v>
+        <v>0.1669122278690338</v>
       </c>
       <c r="FN20" t="n">
-        <v>3.293580812169239e-05</v>
+        <v>0.07369296252727509</v>
       </c>
       <c r="FO20" t="n">
-        <v>4.139136945013888e-05</v>
+        <v>0.01179663091897964</v>
       </c>
       <c r="FP20" t="n">
-        <v>4.008326504845172e-05</v>
+        <v>0.09809864312410355</v>
       </c>
       <c r="FQ20" t="n">
-        <v>2.855907223420218e-05</v>
+        <v>0.1236151307821274</v>
       </c>
       <c r="FR20" t="n">
-        <v>7.860719779273495e-05</v>
+        <v>0.04526906460523605</v>
       </c>
       <c r="FS20" t="n">
-        <v>8.9776556706056e-05</v>
+        <v>0.01268695667386055</v>
       </c>
       <c r="FT20" t="n">
-        <v>7.26435609976761e-05</v>
+        <v>0.268320620059967</v>
       </c>
       <c r="FU20" t="n">
-        <v>3.845117316814139e-05</v>
+        <v>0.4108781218528748</v>
       </c>
       <c r="FV20" t="n">
-        <v>7.942298543639481e-05</v>
+        <v>0.08670045435428619</v>
       </c>
       <c r="FW20" t="n">
-        <v>3.632399966591038e-06</v>
+        <v>0.03294956311583519</v>
       </c>
       <c r="FX20" t="n">
-        <v>3.311339241918176e-05</v>
+        <v>0.008155852556228638</v>
       </c>
       <c r="FY20" t="n">
-        <v>0.0001021419302560389</v>
+        <v>0.1298279017210007</v>
       </c>
       <c r="FZ20" t="n">
-        <v>2.034310637100134e-05</v>
+        <v>0.007652627304196358</v>
       </c>
       <c r="GA20" t="n">
-        <v>5.030962347518653e-05</v>
+        <v>0.08649618178606033</v>
       </c>
       <c r="GB20" t="n">
-        <v>3.197345722583123e-05</v>
+        <v>0.003020565956830978</v>
       </c>
       <c r="GC20" t="n">
-        <v>2.05206852115225e-05</v>
+        <v>0.08036941289901733</v>
       </c>
       <c r="GD20" t="n">
-        <v>5.581208097282797e-05</v>
+        <v>0.01473275944590569</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.0001436285092495382</v>
+        <v>0.1221966445446014</v>
       </c>
       <c r="GF20" t="n">
-        <v>1.074353531294037e-05</v>
+        <v>0.003127872943878174</v>
       </c>
       <c r="GG20" t="n">
-        <v>1.246677766175708e-05</v>
+        <v>0.0824502632021904</v>
       </c>
     </row>
   </sheetData>
